--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
     <row r="9" ht="82" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1243,9 +1243,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1255,42 +1255,42 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Information architecture</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Switched into the Leave view and the Workflows view and catalogued which toolbar controls remain on screen, then pressed one of them.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>The toolbar shows the controls that apply to what is on screen.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>In both views work-scope-mine, work-scope-all and ai-priority-toggle are still visible; clicking All Tasks returns mywork-list. Confirmed on both the Leave and Workflows views at 1440x900.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>The view toggle swaps only the body. The toolbar above it is rendered unconditionally, and the scope / priority handlers each call setView('mywork') as a side effect, so pressing them doubles as an exit.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="10" ht="82" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1337,42 +1337,42 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Information architecture</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Looked for the Leave and Workflows views from My Work on a phone.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>The same two views are reachable from My Work on mobile as on desktop.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>At 390x844 work-view-leave and work-view-workflows are present in the DOM with 0 visible matches. The More panel lists 'Workflows' and 'Leave' as tiles, and /leave loads as its own route.</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The view toggle group is desktop-only, and mobile was given the More panel instead. Both were built; neither was reconciled with the other.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1384,87 +1384,415 @@
     <row r="11" ht="82" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>MW-13</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Workflows view - pipeline cards</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Catalogued every control in the embedded Workflows view and compared their accessible names.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Controls that do different things are distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of workflows-hub: 'Delete card' x5, 'Advance to Delivered' x2, across 21 controls.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>The buttons carry a static label and rely on visual position within their card for meaning.</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="82" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Read the page heading while the Leave view and the Workflows view were open.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>The heading names what is on screen.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot of the Leave view at 1440x900: heading reads 'My Work' above a leave-request list.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>The header is rendered once, outside the view switch.</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="82" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="82" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="82" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>My Work</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1475,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3413,7 +3741,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-090</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3423,7 +3751,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Workflows view (embedded)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3438,12 +3766,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>The Workflows toggle opens the pipelines hub</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -3453,7 +3781,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>workflows-hub renders, 21 controls, 6 stage pipelines with counts</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -3461,7 +3789,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-091</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3471,7 +3799,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Workflows view (embedded)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3481,17 +3809,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>No horizontal overflow and every control has an accessible name</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -3501,7 +3829,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>1440 = 1440; 0 unnamed controls</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -3509,7 +3837,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-092</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3519,7 +3847,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Workflows view (embedded)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3529,17 +3857,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>No dead controls among the non-destructive ones</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -3549,7 +3877,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>6 exercised, all changed state; 10 destructive catalogued not fired</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -3557,7 +3885,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-093</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3567,7 +3895,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Workflows view - card actions</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3577,35 +3905,39 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Controls that do different things are distinguishable by name</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t>'Delete card' x5 and 'Advance to Delivered' x2 share identical names</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>MW-13</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-094</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3615,7 +3947,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Leave view (embedded)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3625,17 +3957,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>The Leave toggle opens the leave surface</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3645,7 +3977,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>My Leave / Approvals tabs, Request Leave, Report Absence, settings all render</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -3653,7 +3985,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-095</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3663,12 +3995,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Leave view (embedded)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3678,12 +4010,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>No horizontal overflow and every control has an accessible name</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3693,7 +4025,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>1440 = 1440; 0 unnamed controls</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -3701,17 +4033,17 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-096</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Leave view (embedded)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3726,49 +4058,45 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>No dead controls among the non-destructive ones</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>10 exercised, all changed state; 1 destructive catalogued not fired</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-097</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Toolbar in Leave / Workflows</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3778,12 +4106,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>The toolbar only offers controls that apply to the active view</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Information architecture</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3793,19 +4121,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
+          <t>New Task, My Tasks, All Tasks and AI Priority all remain; three of them eject you back to the task list when pressed</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-11</t>
         </is>
       </c>
     </row>
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-098</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3815,7 +4143,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Leave / Workflows entry points</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3830,76 +4158,620 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Both views are reachable from My Work on a phone</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Information architecture</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
+          <t>Neither toggle is visible on mobile; both live in the 'More' panel as separate destinations instead</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>MW-12</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>T-099</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Page heading</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>The heading names the view that is on screen</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Orientation</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Heading stays 'My Work' over a leave-request list</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="82" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Standalone /leave route</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Leave is usable on mobile through its own route</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>/leave renders the user's leave records directly</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="82" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="82" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="82" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="82" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="82" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="82" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="82" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="82" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="82" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="82" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>My Work</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4567,7 +5439,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>48 (37 pass, 11 fail, 0 blocked, 0 not run)</t>
+          <t>59 (44 pass, 15 fail, 0 blocked, 0 not run)</t>
         </is>
       </c>
     </row>
@@ -4579,7 +5451,7 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 2 Medium, 1 Low, 2 Nit</t>
+          <t>1 Critical, 4 High, 4 Medium, 2 Low, 3 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -10,12 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified Non-Issues" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action List" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,7 +93,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +113,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -163,6 +175,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5020,6 +5038,1277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>What to change</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Why / evidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Where (code)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="82" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ASK-1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Stage-not-ready override dialog</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Redesign the 'Stage not ready' override popup. It is a plain centred modal with a mono-styled textarea; it should carry the same material as the rest of the redesign, and Override should read as the consequential action.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Founder review of the override flow. Forcing a reason is right -- it goes into workflow history and the audit log -- but the styling predates the current design language and the two actions carry equal visual weight.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>pages/Workflows.js (stage override dialog)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="82" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ASK-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>'Delete card' does nothing</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Replace window.confirm with the in-app confirmation dialog, matching the delete-task-confirm pattern used elsewhere. RBAC needs no change.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED: as owner, clicking Delete produces no dialog, removes no card and issues no DELETE request at all. The handler is wired correctly but sits behind window.confirm, which silently returns false in some browser and embedded contexts. This codebase already hit and fixed exactly this -- FUP-49 removed window.confirm from My Work's Complete button because 'some browsers / embed contexts silently returned without showing UI, so the click looked like a silent no-op'. Workflows still carries the old pattern. RBAC was checked across all four logins and is already correct: only the owner sees Delete (5 buttons); sales, production and finance see none.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>pages/Workflows.js:340 (del handler); precedent at pages/MyWork.js:1108</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="82" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ASK-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>'+ New Task' placement</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Move New Task below the header and stop rendering it outside the task list -- it should not appear while the Leave or Workflows view is open.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Founder: it 'appears all over the place'. Confirmed by MW-11: in the Leave view New Task is the largest, darkest button on screen, and it creates a task rather than a leave request.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>MW-11</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ASK-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Remove per-card 'AI Impact Analysis'</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Remove the AI Impact Analysis button from the individual leave card.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Founder: impact is not a per-request question. Analysing one request in isolation cannot answer what actually matters -- what the combined leave does to cover across the team. Removed now; the global version is ASK-5.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>pages/Leave.js (leave card actions)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="82" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ASK-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Global AI leave-impact analysis</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Future scope</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Reintroduce impact analysis at SECTION level, scoped by period -- this week, this financial year, or just what is pending approval -- so it can answer what the combined leave does to cover.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Founder: the useful question is aggregate, not per-request. Explicitly parked -- not yet ideated, so this is scope to design before it is built.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>(design first)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ASK-4</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Parked - needs design</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ASK-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Leave / Team</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Move Leave into Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Product decision</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Move the Leave surface out of My Work into Team. Only 'Request Leave' stays reachable from a person's own work surface; the register, history and per-department configuration live in Team.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Founder decision, and it matches what the audit found independently. Leave is an HR request-and-approval flow, not task execution: MW-11 shows four task-only controls bleeding into the Leave view with three of them ejecting you, and MW-12 shows the product already disagrees with itself -- on mobile Leave is not in My Work at all, but a separate destination in the More panel.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (view switch), pages/Leave.js, pages/Team.js</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>MW-11, MW-12</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="82" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ASK-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Leave approvals move to the Desk</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Product decision</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Move the leave Approvals queue out of Leave and into the Decision Desk, alongside the rest of the approvals.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Founder decision. Consistent with the audit: an approvals queue carrying 5 pending items currently sits inside a page titled 'My Work', while every other approval in the product is handled on the Desk.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>pages/Leave.js (leave-tab-approvals), pages/Desk.js</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>ASK-6</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="82" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ASK-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Founder review</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Leave / Settings</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Move 'Leave Approvers by Department'</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Needs discussion</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Remove the settings gear from Leave and move 'Leave Approvers by Department' into Settings. RECOMMENDED HOME: Settings &gt; Operations, whose own description is 'Pipelines, stages, task templates and approval gates -- the single source of truth for how work moves'. Leave approval routing is an approval gate, and Settings already owns the money approval threshold under Money. Alternatives considered: Settings &gt; Business (owns roles, but this is routing, not structure) and People &gt; Employees (where a Reporting Manager already overrides this mapping). Suggested resolution: put the control in Operations and show a read-only line on People &gt; Employees pointing at it, so the override and the default are visibly connected without duplicating the control.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Founder: configuration belongs in Settings, not inside a work surface. Placement to be confirmed before the move.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>pages/Leave.js:387-417 (leave-approver-config), :500-510 (gear); pages/Settings.js:150-159 (TABS)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>ASK-6</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Awaiting decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="82" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MW-08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Task card - Update / Escalate</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="82" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MW-09</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="82" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MW-10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Application shell</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="82" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MW-01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Task card - status control</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="82" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MW-02</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Task card - detail dialog</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="82" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Header - global search (Cmd+K)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="82" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker (mobile)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>components/mobile/DexFab.jsx:70-82</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="82" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MW-11</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Toolbar in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MW-12</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Leave and Workflows entry points</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="82" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MW-13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Workflows view - pipeline cards</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="82" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="82" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="82" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="82" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MW-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Task card - Complete (evidence required)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>By design</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1107-1119</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Not a defect</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5028,7 +6317,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>DecisionOS - UI / UX audit standard</t>
         </is>
@@ -5040,380 +6329,380 @@
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr"/>
+      <c r="B3" s="14" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>One workbook for the whole DecisionOS UI audit. Every screen is tested on mobile and desktop, across personas, and every finding lands here with the evidence that proves it and the fix that would close it.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr"/>
-      <c r="B5" s="12" t="inlineStr"/>
+      <c r="A5" s="13" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Bug Log</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Confirmed defects. One row per defect, with root cause and a proposed solution. This is the sheet to work from.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Test Coverage</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Everything that was tested and how it came out, so the gaps are as visible as the failures.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Verified Non-Issues</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Things that looked like defects and were disproved. Kept on purpose so nobody spends the afternoon re-finding them.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr"/>
-      <c r="B10" s="12" t="inlineStr"/>
+      <c r="A10" s="13" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Data loss, a security hole, or the section cannot be used at all.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>A core action is broken, silently wrong, or entirely missing.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Works, but a real group of users is blocked or misled - accessibility failures live here.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Visible imperfection with no functional cost.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Polish. Safe to close as won't-fix if priorities are elsewhere.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr"/>
-      <c r="B17" s="12" t="inlineStr"/>
+      <c r="A17" s="13" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Confirmed and not yet fixed.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Behaviour is intentional; any row here is a suggestion, not a defect.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Corrected and re-tested - record the re-test in Test Coverage.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Accepted as-is. Say why in the row.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="12" t="inlineStr"/>
+      <c r="A23" s="13" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Result values (Test Coverage)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr"/>
+      <c r="B24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Behaved as expected.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Did not - must link to a Bug Log ID.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Could not be judged because another defect got in the way.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Deliberately not run - say why (for example destructive against shared data).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr"/>
-      <c r="B29" s="12" t="inlineStr"/>
+      <c r="A29" s="13" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Ground rules</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr"/>
+      <c r="B30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Every FAIL carries a measurement, a response body, or a screenshot. No finding is filed on impression alone.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Disprove first</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Anything that looks wrong is re-measured before it is filed. The Verified Non-Issues sheet is the record of that step.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Shared data</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Destructive actions are never fired blind against the shared dev database. Test rows are tagged and deleted afterwards.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Regenerating</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>This file is rebuilt from backend/scripts/build_ui_bug_report.py. Edit the tables in that script, not the spreadsheet, so the two never drift apart.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr"/>
-      <c r="B35" s="12" t="inlineStr"/>
+      <c r="A35" s="13" t="inlineStr"/>
+      <c r="B35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Artifacts</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr"/>
+      <c r="B36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Screenshots</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>.audit-artifacts/ux/&lt;section&gt;/&lt;viewport&gt;/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Raw reports</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>.audit-artifacts/ux/&lt;section&gt;/report.json</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Harness</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>backend/scripts/ux_audit.py (layout, a11y, console, control sweep)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr"/>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>backend/scripts/ux_flow_mywork.py (filters and lenses do the right thing)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr"/>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>backend/scripts/ux_lifecycle_mywork.py (create to delete, every persona)</t>
         </is>
@@ -5424,7 +6713,7 @@
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Run summary - My Work</t>
         </is>
@@ -5432,72 +6721,72 @@
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Checks run</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>59 (44 pass, 15 fail, 0 blocked, 0 not run)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Defects</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>1 Critical, 4 High, 4 Medium, 2 Low, 3 Nit</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Non-issues disproved</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Viewports</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Mobile 390x844 and Desktop 1440x900</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Owner, Sales, Production, Finance</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Audited on</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>2026-09-12, branch karma-redesign</t>
         </is>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5038,7 +5038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5558,12 +5558,12 @@
     <row r="10" ht="82" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5573,35 +5573,39 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Task expanded view + 'Log update or hand off'</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Redesign the expanded task view, and rework the 'Log update or hand off' control at the bottom of it -- both how it looks and the fact that it does not work. Today it is a quiet text link in the bottom-right corner, which is the wrong weight for the one action that records what happened on a task and hands it to someone else. Fixing the crash (MW-08) and wiring the mobile twin (MW-09) are prerequisites, not the whole job.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>VERIFIED on the exact control the founder pointed at. On desktop it is add-update-&lt;id&gt;, labelled 'Log update or hand off' -- clicking it renders no form, throws 'CTRL_ON is not defined' and leaves the React root empty, so the whole app goes down. Its mobile twin log-update-m-&lt;id&gt; carries the same label and has no onClick at all. Between them there is no working way to log an update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>pages/MyWork.js:147 (crash), :195/:207 (desktop button), :1496-1505 (mobile)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>MW-08, MW-09</t>
+        </is>
+      </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -5611,12 +5615,12 @@
     <row r="11" ht="82" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>ASK-10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5626,12 +5630,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Multi-select bar</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
+          <t>Change request</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -5641,17 +5645,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Rework the multi-select action bar. Two of its three actions are close to unreadable and one is too small to hit comfortably.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>MEASURED, not impression. The bar is near-black (bg-kr-ink) with white text. 'Complete' was re-themed for that dark ground (black on a white pill, 19.6:1) and reads correctly. The other two were left on light-theme tokens: 'Reassign' uses bg-nm / nm-btn -- a light grey #E9EAEC surface -- while inheriting the bar's white text, giving white-on-light-grey at 1.2:1; 'Clear' uses text-muted-foreground, a light-theme grey #585551, on the near-black bar at 2.64:1. WCAG AA needs 4.5:1. 'Clear' is also only 45x16px, under the 24px minimum hit size. Selection counting and pluralisation are correct ('2 selected / Complete 2'), so the logic is sound - this is purely the dark-bar treatment being applied to one button out of three.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/MyWork.js:918-962 (bulk-action-bar; bulk-reassign :946, bulk-clear :955)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -5664,7 +5668,7 @@
     <row r="12" ht="82" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5674,12 +5678,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -5687,24 +5691,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -5717,7 +5721,7 @@
     <row r="13" ht="82" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5747,17 +5751,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -5770,7 +5774,7 @@
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5780,12 +5784,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5800,17 +5804,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -5823,7 +5827,7 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -5833,12 +5837,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5846,24 +5850,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -5876,7 +5880,7 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -5886,12 +5890,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5899,24 +5903,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -5929,7 +5933,7 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -5939,12 +5943,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5959,17 +5963,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -5982,7 +5986,7 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -5992,12 +5996,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6012,17 +6016,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -6035,7 +6039,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -6050,7 +6054,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6058,24 +6062,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -6088,7 +6092,7 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6103,7 +6107,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6111,24 +6115,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -6141,7 +6145,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -6156,7 +6160,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -6164,24 +6168,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -6194,7 +6198,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6209,7 +6213,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6217,24 +6221,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -6247,58 +6251,164 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="82" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="82" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>My Work</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K23"/>
+  <autoFilter ref="A1:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5038,7 +5038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>VERIFIED: as owner, clicking Delete produces no dialog, removes no card and issues no DELETE request at all. The handler is wired correctly but sits behind window.confirm, which silently returns false in some browser and embedded contexts. This codebase already hit and fixed exactly this -- FUP-49 removed window.confirm from My Work's Complete button because 'some browsers / embed contexts silently returned without showing UI, so the click looked like a silent no-op'. Workflows still carries the old pattern. RBAC was checked across all four logins and is already correct: only the owner sees Delete (5 buttons); sales, production and finance see none.</t>
+          <t>VERIFIED: as owner, clicking Delete produces no dialog, removes no card and issues no DELETE request at all. The handler is wired correctly but sits behind window.confirm, which silently returns false in some browser and embedded contexts -- the exact failure FUP-49 already documented when it removed window.confirm from My Work's Complete button for looking like 'a silent no-op'. Workflows still carries the old pattern. RBAC was checked across all four logins and is already correct: only the owner sees Delete (5 buttons); sales, production and finance see none.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Move 'Leave Approvers by Department'</t>
+          <t>DELETE 'Leave Approvers by Department' (do not move it)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Needs discussion</t>
+          <t>Product decision</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Remove the settings gear from Leave and move 'Leave Approvers by Department' into Settings. RECOMMENDED HOME: Settings &gt; Operations, whose own description is 'Pipelines, stages, task templates and approval gates -- the single source of truth for how work moves'. Leave approval routing is an approval gate, and Settings already owns the money approval threshold under Money. Alternatives considered: Settings &gt; Business (owns roles, but this is routing, not structure) and People &gt; Employees (where a Reporting Manager already overrides this mapping). Suggested resolution: put the control in Operations and show a read-only line on People &gt; Employees pointing at it, so the override and the default are visibly connected without duplicating the control.</t>
+          <t>Founder asked whether this setting is needed at all, given the approver is already chosen when a team member is added. VERIFIED ANSWER: it is not. Recommendation is now to DELETE the screen and the tenant mapping behind it, not relocate it into Settings. Keep the two tiers that carry real meaning -- the member's reporting manager, then the owner.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Founder: configuration belongs in Settings, not inside a work surface. Placement to be confirmed before the move.</t>
+          <t>The resolver runs reporting manager, then the department mapping, then the owner (services/leave.py:_resolve_leave_approver). Team.js:144 already has a Reporting Manager picker on both add and edit, so tier 1 is set where the person is created. Measured against live data: of 12 members, 1 has a reporting manager and the tenant mapping is EMPTY, so 11 of 12 resolve straight to the owner and the middle tier is used by nobody. A settings screen that configures a tier no one reaches is a third place to express the same decision, and the most likely outcome of keeping it is a mapping that quietly disagrees with the org chart. If some department genuinely needs an approver who is not the member's manager, the honest fix is to set that person as their reporting manager.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>pages/Leave.js:387-417 (leave-approver-config), :500-510 (gear); pages/Settings.js:150-159 (TABS)</t>
+          <t>services/leave.py:_resolve_leave_approver; pages/Team.js:144 (member-manager-select); pages/Leave.js:387-417 + :500-510 (to remove); routers/calendar.py:24 (PATCH /tenant/leave-approvers)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Task expanded view + 'Log update or hand off'</t>
+          <t>Redesign the expanded task card (whole surface)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Redesign the expanded task view, and rework the 'Log update or hand off' control at the bottom of it -- both how it looks and the fact that it does not work. Today it is a quiet text link in the bottom-right corner, which is the wrong weight for the one action that records what happened on a task and hands it to someone else. Fixing the crash (MW-08) and wiring the mobile twin (MW-09) are prerequisites, not the whole job.</t>
+          <t>Rework the UI and UX of the expanded task card end to end, not control by control. Today it stacks description, a status line, a progress rail, a status dropdown, a '% manually' disclosure, a Complete button, an Attach row, a plan row and an activity footer -- nine bands with no grouping, and the one action that records what happened is a quiet text link in the bottom-right corner. Group it into what the task IS, where it stands, and what you do next. ASK-11 and ASK-12 are the two specific decisions inside this redesign.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>VERIFIED on the exact control the founder pointed at. On desktop it is add-update-&lt;id&gt;, labelled 'Log update or hand off' -- clicking it renders no form, throws 'CTRL_ON is not defined' and leaves the React root empty, so the whole app goes down. Its mobile twin log-update-m-&lt;id&gt; carries the same label and has no onClick at all. Between them there is no working way to log an update or hand a task off on either viewport.</t>
+          <t>Founder review. Reinforced by what the audit already found on this exact surface: the log / hand-off control crashes the app (MW-08), its mobile twin is inert (MW-09), and the status and progress controls do not reflect their own changes until a reload (MW-01).</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (crash), :195/:207 (desktop button), :1496-1505 (mobile)</t>
+          <t>pages/MyWork.js:1295-1800 (expanded body, mobile + desktop)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>MW-08, MW-09</t>
+          <t>MW-01, MW-08, MW-09</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Multi-select bar</t>
+          <t>Multi-select bar: contrast + wording</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Rework the multi-select action bar. Two of its three actions are close to unreadable and one is too small to hit comfortably.</t>
+          <t>Two fixes. (1) Readability: re-theme the bar's actions for its dark ground. (2) Wording: 'Reassign' here and 'hand off' on the task card are the same act -- give the work to someone else -- so settle on ONE verb and use it in both places, in the bulk bar, on the card, and in the activity trail.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>MEASURED, not impression. The bar is near-black (bg-kr-ink) with white text. 'Complete' was re-themed for that dark ground (black on a white pill, 19.6:1) and reads correctly. The other two were left on light-theme tokens: 'Reassign' uses bg-nm / nm-btn -- a light grey #E9EAEC surface -- while inheriting the bar's white text, giving white-on-light-grey at 1.2:1; 'Clear' uses text-muted-foreground, a light-theme grey #585551, on the near-black bar at 2.64:1. WCAG AA needs 4.5:1. 'Clear' is also only 45x16px, under the 24px minimum hit size. Selection counting and pluralisation are correct ('2 selected / Complete 2'), so the logic is sound - this is purely the dark-bar treatment being applied to one button out of three.</t>
+          <t>MEASURED. The bar is near-black (bg-kr-ink) with white text. 'Complete' was re-themed for that ground (black on a white pill, 19.6:1) and reads fine. The other two were left on light-theme tokens: 'Reassign' uses bg-nm / nm-btn -- a light grey #E9EAEC surface -- while inheriting the bar's white text, giving white-on-light-grey at 1.2:1; 'Clear' uses text-muted-foreground, a light-theme grey #585551, on the near-black bar at 2.64:1. WCAG AA wants 4.5:1. 'Clear' is also only 45x16px, under the 24px hit minimum. Counting and pluralisation are correct ('2 selected / Complete 2'), so none of this is logic -- the dark-bar treatment reached one button out of three. On wording, the founder's point stands: the product currently calls the same action 'Reassign' in bulk and 'hand off' on the card.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:918-962 (bulk-action-bar; bulk-reassign :946, bulk-clear :955)</t>
+          <t>pages/MyWork.js:918-962 (bulk-action-bar; bulk-reassign :946, bulk-clear :955); card wording at :195/:207</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -5668,12 +5668,12 @@
     <row r="12" ht="82" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5683,35 +5683,39 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>'Complete' exists twice -- button and dropdown</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Take the terminal states out of the desktop status dropdown. It currently offers Completed and Cancelled alongside the four in-flight states, while Complete is also its own button and Cancel is its own button -- two routes to the same ending, and the dropdown route gives none of the confirmation or the proof prompt the button does.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>Founder asked why Complete appears in both places. The team already decided this once, for mobile: MyWork.js:1594 records that Completed and Cancelled were removed from the mobile status pills because both are TERMINAL, so choosing either 'removed the task from the list the bar was sitting in -- the control deleted its own context', noting Complete already has its own button. That reasoning was applied to the mobile pills and never carried across to the desktop dropdown, which still lists all six. Tested for a worse version of this -- whether the dropdown lets you finish a task that requires proof -- and it does not: both routes correctly refused to complete an evidence-required task. So this is redundancy and inconsistency, not a hole.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>pages/MyWork.js:79-86 (STATUS_OPTIONS), :1602 (desktop select), :102-108 + :1594 (the mobile decision and its reasoning)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ASK-9</t>
+        </is>
+      </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -5721,12 +5725,12 @@
     <row r="13" ht="82" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>ASK-12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -5736,35 +5740,39 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Put logging where the work is</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Move logging up next to Attach, so the row reads as one act: attach a photo, a file, a voice note -- or write what happened. Escalate and hand off then become choices WITHIN that one flow rather than separate controls elsewhere on the card, which is what the underlying form already models.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>Founder direction, and the code already agrees. UpdateForm takes an action of exactly this shape -- a note plus a choice of update, escalate or hand off, with a person picker appearing for hand-off -- so the three are already one flow in the data model and only look like separate features on screen. Today the entry point sits far from Attach, in the footer, as the lightest control on the card despite recording the most important thing.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>pages/MyWork.js:111-166 (UpdateForm + its ACTIONS), :1740-1780 (attach row), :195/:207 (current entry point)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ASK-9</t>
+        </is>
+      </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -5774,7 +5782,7 @@
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5784,12 +5792,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5797,24 +5805,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -5827,7 +5835,7 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -5842,7 +5850,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5857,17 +5865,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -5880,7 +5888,7 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -5890,12 +5898,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5910,17 +5918,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -5933,7 +5941,7 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -5943,12 +5951,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5956,24 +5964,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -5986,7 +5994,7 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -5996,12 +6004,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6009,24 +6017,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -6039,7 +6047,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -6049,12 +6057,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6069,17 +6077,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -6092,7 +6100,7 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -6102,12 +6110,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6122,17 +6130,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -6145,7 +6153,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -6160,7 +6168,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -6168,24 +6176,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -6198,7 +6206,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6213,7 +6221,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6221,24 +6229,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -6251,7 +6259,7 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -6266,7 +6274,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -6274,24 +6282,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -6304,7 +6312,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6319,7 +6327,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6327,24 +6335,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -6357,58 +6365,164 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="82" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="82" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>My Work</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:K27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified Non-Issues" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action List" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +80,11 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
@@ -122,7 +128,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -180,19 +186,34 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5531,7 +5552,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Founder asked whether this setting is needed at all, given the approver is already chosen when a team member is added. VERIFIED ANSWER: it is not. Recommendation is now to DELETE the screen and the tenant mapping behind it, not relocate it into Settings. Keep the two tiers that carry real meaning -- the member's reporting manager, then the owner.</t>
+          <t>PARKED - Yogesh is taking this decision himself, later. Do not action it. The reasoning is written up in full on the 'Notes &amp; Decisions' sheet. Summary of the recommendation as it stands: founder asked whether this already chosen when a team member is added. VERIFIED ANSWER: it is not. Recommendation is now to DELETE the screen and the tenant mapping behind it, not relocate it into Settings. Keep the two tiers that carry real meaning -- the member's reporting manager, then the owner.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -5551,7 +5572,7 @@
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>Awaiting decision</t>
+          <t>Deferred - founder</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6554,501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="116" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr"/>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Leave approvals: who approves, and is the Settings screen needed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="12" t="inlineStr"/>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Raised 2026-09-12 by Yogesh - Owner. Status: DEFERRED, Yogesh deciding. Relates to ASK-8. Nothing is to be built from this note until that call is made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>THE QUESTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="15" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Leave approval is mostly done by either the owner or a manager. The approver is already chosen when a team member is added. So does the 'Leave Approvers by Department' settings screen need to exist at all?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="17" t="inlineStr"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>HOW APPROVAL IS DECIDED TODAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>When someone requests leave the system asks three questions IN ORDER and stops at the first that answers. The code is services/leave.py, _resolve_leave_approver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Does this person have a Reporting Manager? If yes, that manager approves. The Reporting Manager is chosen in Team when the member is added or edited (pages/Team.js:144, the member-manager-select dropdown; stored as reporting_manager_id).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Otherwise: is there a department rule for their role? If yes, that person approves. THIS IS THE SETTINGS SCREEN under discussion - the gear in the Leave section, which opens 'Leave Approvers by Department' with one dropdown per department and a Save button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Otherwise the Owner approves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>WHAT THE LIVE DATA SHOWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr"/>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Measured against the dev workspace on 2026-09-12, not assumed:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>12 team members in the workspace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1 used</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>1 member has a Reporting Manager set (sai, finance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2 used</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>0. The tenant leave_approvers mapping is EMPTY - every department reads 'Owner (default)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Tier 3 used</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>11 of 12 members fall through to the Owner, Rajesh Sharma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>So</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>The Settings screen currently decides leave for NOBODY. It configures a tier that no request reaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr"/>
+      <c r="B20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="17" t="inlineStr"/>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>WHAT THE THREE PIECES ARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="15" t="inlineStr"/>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>They are three layers of one feature. Removing one without the others leaves either a screen that cannot save or an endpoint nothing calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>The gear</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>The small round icon beside the My Leave / Approvals tabs. It is the only way into the screen. pages/Leave.js:500-510.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>The panel</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>'Leave Approvers by Department' - a dropdown per department plus a Save approvers button. pages/Leave.js:387-417.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>The endpoint</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>PATCH /tenant/leave-approvers, which writes the leave_approvers field on the tenant record. routers/calendar.py:24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr"/>
+      <c r="B26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="17" t="inlineStr"/>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>OPTION A - DELETE TIER 2  (the current recommendation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>What changes</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Remove the gear, the panel and the endpoint. Approval becomes: reporting manager, else owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Effect today</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>NONE. Every one of the 12 members resolves to exactly the same approver before and after, because nothing uses tier 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Argument for</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>The approver is already chosen once, in Team, when the person is added. A second screen expressing the same decision in different words - and silently losing to the first one - mostly creates the chance for the two to disagree with the org chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr"/>
+      <c r="B31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="17" t="inlineStr"/>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>OPTION B - KEEP TIER 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>What it buys</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>One place to say 'all Sales leave goes to Priya' without making Priya anyone's reporting manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Cost of A</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>To get that same outcome after deleting, Priya would have to be set as the reporting manager of each Sales person individually, in Team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>If kept</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Then the fix is not to move it into Settings but to make it visible - today it is hidden behind an unlabelled gear inside a work surface, which is why it has stayed empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr"/>
+      <c r="B36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="17" t="inlineStr"/>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>THE ONE QUESTION THAT DECIDES IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr"/>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Is 'who approves your leave' always the same person as 'who you report to'?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>They are always the same -&gt; Option A. Tier 2 is pure duplication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>They can differ - for example a department lead signs off leave while people report to a project manager -&gt; Option B, and the work is to surface the screen properly rather than hide it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>For an SME the answer is usually yes, which is why A is the standing recommendation - but this is a business call, not a technical one, which is why it is parked rather than filed as a defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="17" t="inlineStr"/>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>IF OPTION A IS CHOSEN, THE WORK IS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Delete the gear and the settings tab from pages/Leave.js (:500-510).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Delete the LeaveApproverConfig block from pages/Leave.js (:387-417).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Delete PATCH /tenant/leave-approvers from routers/calendar.py (:24) and the LeaveApproverMapInput model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Drop the tier-2 lookup from _resolve_leave_approver in services/leave.py, leaving reporting manager then owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Leave the leave_approvers field on existing tenant records alone, or clear it in the migration - it is empty in practice either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Make sure Team makes the consequence visible: the Reporting Manager dropdown should say that this person also approves their leave, since after this change that is the only place the decision is made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>This depends on ASK-6. If Leave moves into Team first, the gear disappears with it and steps 1 and 2 become part of that move rather than separate work.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6541,7 +7056,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>DecisionOS - UI / UX audit standard</t>
         </is>
@@ -6553,464 +7068,488 @@
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr"/>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>One workbook for the whole DecisionOS UI audit. Every screen is tested on mobile and desktop, across personas, and every finding lands here with the evidence that proves it and the fix that would close it.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="A5" s="15" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Bug Log</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Confirmed defects. One row per defect, with root cause and a proposed solution. This is the sheet to work from.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Test Coverage</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Everything that was tested and how it came out, so the gaps are as visible as the failures.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Verified Non-Issues</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Things that looked like defects and were disproved. Kept on purpose so nobody spends the afternoon re-finding them.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Action List</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Everything to be done in one list - the founder's change asks first, then every defect by severity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Notes &amp; Decisions</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>The reasoning behind calls that were parked rather than taken, written so they can be picked up cold weeks later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Data loss, a security hole, or the section cannot be used at all.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>A core action is broken, silently wrong, or entirely missing.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Works, but a real group of users is blocked or misled - accessibility failures live here.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Visible imperfection with no functional cost.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Polish. Safe to close as won't-fix if priorities are elsewhere.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr"/>
-      <c r="B17" s="14" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr"/>
+      <c r="B19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Confirmed and not yet fixed.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Behaviour is intentional; any row here is a suggestion, not a defect.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Corrected and re-tested - record the re-test in Test Coverage.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Won't fix</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Accepted as-is. Say why in the row.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr"/>
-      <c r="B23" s="14" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr"/>
+      <c r="B25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Result values (Test Coverage)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Behaved as expected.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Did not - must link to a Bug Log ID.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Could not be judged because another defect got in the way.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Deliberately not run - say why (for example destructive against shared data).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr"/>
-      <c r="B29" s="14" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr"/>
+      <c r="B31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Ground rules</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Every FAIL carries a measurement, a response body, or a screenshot. No finding is filed on impression alone.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Disprove first</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Anything that looks wrong is re-measured before it is filed. The Verified Non-Issues sheet is the record of that step.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Shared data</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Destructive actions are never fired blind against the shared dev database. Test rows are tagged and deleted afterwards.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Regenerating</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>This file is rebuilt from backend/scripts/build_ui_bug_report.py. Edit the tables in that script, not the spreadsheet, so the two never drift apart.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr"/>
-      <c r="B35" s="14" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr"/>
+      <c r="B37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Artifacts</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Screenshots</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>.audit-artifacts/ux/&lt;section&gt;/&lt;viewport&gt;/</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Raw reports</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>.audit-artifacts/ux/&lt;section&gt;/report.json</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Harness</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>backend/scripts/ux_audit.py (layout, a11y, console, control sweep)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr"/>
-      <c r="B40" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>backend/scripts/ux_flow_mywork.py (filters and lenses do the right thing)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr"/>
-      <c r="B41" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>backend/scripts/ux_lifecycle_mywork.py (create to delete, every persona)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Run summary - My Work</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Checks run</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B46" s="22" t="inlineStr">
         <is>
           <t>59 (44 pass, 15 fail, 0 blocked, 0 not run)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Defects</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>1 Critical, 4 High, 4 Medium, 2 Low, 3 Nit</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>Non-issues disproved</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B48" s="22" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>Viewports</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B49" s="22" t="inlineStr">
         <is>
           <t>Mobile 390x844 and Desktop 1440x900</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>Owner, Sales, Production, Finance</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>Audited on</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>2026-09-12, branch karma-redesign</t>
         </is>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1587,27 +1587,27 @@
     <row r="13" ht="82" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1622,42 +1622,42 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Opened Add member and pressed both halves of the Password login / Mobile OTP toggle, checking what each exposes to assistive technology.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>The selected login method is announced, as the permission toggles in the same dialog already are.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Team.js:165 gives every perm-&lt;key&gt; toggle aria-pressed={on}; the two login-method buttons at :123 and :125 set className only. Pressing the already-active half produced no detectable state change of any kind.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>The toggle was styled as a segmented control but never given the ARIA the rest of the same file uses.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1704,42 +1704,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1751,87 +1751,415 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="82" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="82" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="82" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P15"/>
+  <autoFilter ref="A1:P19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1842,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4324,12 +4652,12 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-200</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4349,12 +4677,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>/team loads directly with the full roster</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -4364,7 +4692,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>12 members grouped by role; no redirect</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -4372,12 +4700,12 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-201</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4387,22 +4715,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>/team loads and reflows to a single column</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -4412,7 +4740,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>224 visible elements, 20 interactive, no layout break</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -4420,37 +4748,37 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-202</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>No horizontal overflow on either viewport</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -4460,7 +4788,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>desktop 1440=1440, mobile 390=390</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -4468,37 +4796,37 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-203</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Every control meets the 24px tap-target minimum</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -4508,7 +4836,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>0 under 24px</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -4516,37 +4844,37 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-204</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>All text</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>All interactive text meets 4.5:1 contrast</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -4556,7 +4884,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>0 below 4.5:1 on either viewport</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -4564,17 +4892,17 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-205</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4589,12 +4917,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Every button and link has an accessible name</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4604,7 +4932,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>0 unnamed; 0 images missing alt</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -4612,17 +4940,17 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-206</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4637,44 +4965,40 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>15 pressed incl. every dialog descended into; 0 crashes</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="82" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-207</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4689,49 +5013,45 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>10 pressed incl. dialogs; 0 crashes, 0 dead controls</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="82" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-208</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4741,12 +5061,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Every nav destination routes correctly</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -4756,7 +5076,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
+          <t>desktop rail and mobile dock both resolve; aria-current set on Team</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -4764,53 +5084,1181 @@
     <row r="60" ht="82" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>T-209</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Add member dialog</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Add member opens a complete form</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>6 fields, 18 controls: name, email, login method, password, phone, role, manager, permission grid, menu preview</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="82" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>T-210</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Add member validation</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>An empty form is refused with a clear reason</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>No API call fired; dialog stayed open; 'Name and email are required'</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="82" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>T-211</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Add member - login method</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>The selected login method is exposed to assistive technology</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>No aria-pressed on either half of the toggle</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>TM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="82" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>T-212</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>A member card opens their profile with contact, reporting line and access</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Shows CONTACT, REPORTS TO, and ACCESS as 'n of 14 areas' with the list</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="82" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>T-213</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>The dialog has a proper accessible name</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>sr-only DialogHeader + DialogTitle at Team.js:497 - the pattern MW-03 lacks</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="82" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>T-214</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Every control in the dialog is distinguishable by name</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Two visible buttons both named 'Close'</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="82" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>T-215</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Edit access</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Edit access opens the permission editor in place</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Dialog content grows 1411 to 2299 chars; no error</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="82" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>T-216</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Get invite link</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>The invite control is present, unobstructed and correctly gated</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Rendered only for non-owners who have a phone; clickable and not covered</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="82" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>T-217</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Get invite link</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>An invite link is generated end to end</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>NOT RUN by choice - it would mint a real invite token for a live teammate. The only disposable accounts have no phone, so the control is correctly hidden for them. Needs one manual pass.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="82" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>T-218</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>The owner can add and manage members</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Add member visible; no view-only banner</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="82" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>T-219</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Sales / Production / Finance</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Non-managers see the roster but cannot change it</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>All three: 12 cards visible, Add member hidden, view-only banner shown, no page errors</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="82" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>T-220</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Role groups fill their row</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Owner group is a 3-column grid holding one card; 874 of 1336px empty</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="82" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>T-221</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>The roster shows what its own heading promises</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Information architecture</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Eyebrow says EMPLOYEES / ACCESS / REPORTING LINES; cards show neither the reporting line nor what the access is, only a count</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="82" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>T-222</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>No application errors and no failing API calls</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="82" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="82" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="82" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="82" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="82" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="82" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="82" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="82" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="82" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="82" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J60"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5059,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6333,7 +7781,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -6343,12 +7791,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6363,17 +7811,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -6386,7 +7834,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -6401,7 +7849,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -6409,24 +7857,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -6439,7 +7887,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -6454,7 +7902,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6469,17 +7917,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -6492,58 +7940,270 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="82" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="82" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="82" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="82" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K27"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7491,7 +9151,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>59 (44 pass, 15 fail, 0 blocked, 0 not run)</t>
+          <t>82 (62 pass, 19 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -7503,7 +9163,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 4 Medium, 2 Low, 3 Nit</t>
+          <t>1 Critical, 4 High, 4 Medium, 3 Low, 6 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1669,7 @@
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1692,9 +1692,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1704,42 +1704,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Information disclosure</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Signed in as each of the four roles in turn and opened ANOTHER person's member card, to see how much of their access is readable.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>A person's permission set is visible to those who administer access, not to every colleague.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>owner / sales / production / finance all returned ACCESS block=True, areaCount=True, denialList=True on a colleague's profile; only editAccess differed (owner True, the rest False).</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>canManageTeam gates the edit control, but the ACCESS section and the card count render unconditionally.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1786,42 +1786,42 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1868,42 +1868,42 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1915,32 +1915,32 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>Each control in a dialog is distinguishable by name.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -2032,42 +2032,42 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Visual / alignment</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2079,87 +2079,169 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="82" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P19"/>
+  <autoFilter ref="A1:P20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2170,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5772,17 +5854,17 @@
     <row r="74" ht="82" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-223</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Member profile - ACCESS</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5792,12 +5874,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales / Production / Finance</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>A colleague's permission set is not readable by people who do not administer it</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -5805,22 +5887,26 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+          <t>All four roles can read another member's full matrix: count, granted chips and the complete 'No access to' denial list. Only the Edit button is gated.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>TM-05</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-070</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5840,12 +5926,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -5860,7 +5946,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -5868,7 +5954,7 @@
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-071</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5888,12 +5974,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5908,7 +5994,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -5916,7 +6002,7 @@
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-072</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5936,12 +6022,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Production sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5956,7 +6042,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -5964,7 +6050,7 @@
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-073</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5984,17 +6070,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Finance sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -6004,7 +6090,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -6012,7 +6098,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-074</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -6022,22 +6108,22 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>No uncaught page errors for any persona</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6052,7 +6138,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>0 page errors across owner, sales, production and finance</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -6060,22 +6146,22 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-080</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Console + network</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6085,34 +6171,30 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>No application console errors and no failing API calls in normal use</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-081</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -6122,12 +6204,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Global search dialog</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6137,7 +6219,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>Opening global search logs no accessibility errors</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6152,29 +6234,29 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
+          <t>Radix logs a missing DialogTitle error on every open</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
     </row>
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-082</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Dex FAB picker</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6189,76 +6271,128 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>The picker closes on Escape</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="82" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6507,7 +6641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7251,50 +7385,54 @@
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Stop showing access on the Team roster</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Take the access read-out off the Team surface. It appears in three places: the 'N permissions' line on every card, the 'n of 14 areas' count in the profile dialog, and the full 'No access to ...' denial list beneath it.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>Founder direction, and the audit found it is also an exposure. Verified across all four logins: every role can open any colleague's card and read their complete permission matrix, including everything they are denied. Only the Edit button is gated; the display is not. See TM-05.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+          <t>pages/Team.js:411 + :441 (card), :580-606 (dialog ACCESS block)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>TM-05</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -7304,47 +7442,47 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>ASK-14</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Redesign the Add team member dialog</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Rework the Add member form. It is one long scroll of eight controls with no grouping, ending in a fourteen-item permission checklist, and the submit button sits below the fold. Group it into who they are, how they sign in, where they sit, and what they can reach.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>Founder review. Two concrete problems back it up. First, the first four fields (Name, Email, Temp password, Mobile number) use placeholders INSTEAD of labels, so the moment you type the field name disappears -- while Role and Reporting Manager directly below them do have real labels, so the form is inconsistent with itself. Second, access is chosen from a flat list of fourteen checkboxes at the bottom of a scrolling dialog, which is the densest part of the form and the least explained.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/Team.js:118-196 (member form); placeholder-only inputs at :120, :121, :129, :132; real labels at :137 and :143</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -7357,27 +7495,27 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>ASK-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Gate Edit access on the People permission</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
+          <t>Change request</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -7387,20 +7525,24 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Show Edit access to holders of the 'people' permission (People / Contacts), rather than to team_manage alone as it does today.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>Founder direction. Note for whoever picks this up: 'people' is currently described in the code as opt-in because the contact list is sensitive, and it is NOT in any role's default set -- so on today's data this would show the control to nobody but the owner, who passes through the role check anyway. Worth confirming whether the intent is to REPLACE the team_manage gate with people, or to allow either.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>pages/Team.js:232 (canManageTeam), :571 (edit-access-&lt;id&gt;); lib/perms.js:5 (the 'people' key) and :21-23 (why it is opt-in)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ASK-13</t>
+        </is>
+      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -7410,60 +7552,64 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>ASK-16</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Org chart from reporting lines and department</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Future scope</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Render the team as an organisation chart -- grouped by department and wired by reporting line -- in the style of Microsoft Teams, alongside or instead of the current flat role groups.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>Founder idea, marked 'if needed'. The data already exists: members carry reporting_manager_id and a role, and the profile dialog already resolves and displays 'REPORTS TO'. It also answers TM-03, where the page promises REPORTING LINES and the roster never shows them. Worth noting before building: only 1 of 12 members currently has a reporting manager set, so a chart drawn today would be one line and eleven orphans -- the chart is only as good as the reporting data behind it, and that needs filling first.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>pages/Team.js:475 (manager already resolved); reporting_manager_id on the user record</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Parked - needs design</t>
         </is>
       </c>
     </row>
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7478,7 +7624,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7486,24 +7632,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -7516,7 +7662,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -7526,12 +7672,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7539,24 +7685,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -7569,7 +7715,7 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7584,7 +7730,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7592,24 +7738,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -7622,7 +7768,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7637,7 +7783,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -7645,24 +7791,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -7675,7 +7821,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -7690,7 +7836,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -7698,24 +7844,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -7728,7 +7874,7 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7738,12 +7884,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -7751,24 +7897,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -7781,7 +7927,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7791,12 +7937,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7804,24 +7950,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -7834,7 +7980,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7849,7 +7995,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -7857,24 +8003,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -7887,7 +8033,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -7902,7 +8048,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -7910,24 +8056,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -7940,7 +8086,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -7955,7 +8101,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -7963,24 +8109,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -7993,7 +8139,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8003,12 +8149,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8016,24 +8162,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -8046,7 +8192,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -8061,7 +8207,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8069,24 +8215,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -8099,7 +8245,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8114,7 +8260,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8122,24 +8268,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -8152,58 +8298,323 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="82" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="82" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="82" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="82" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="82" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K31"/>
+  <autoFilter ref="A1:K36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9151,7 +9562,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>82 (62 pass, 19 fail, 0 blocked, 1 not run)</t>
+          <t>83 (62 pass, 20 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9574,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 4 Medium, 3 Low, 6 Nit</t>
+          <t>1 Critical, 4 High, 5 Medium, 3 Low, 6 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1751,7 +1751,7 @@
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1786,42 +1786,42 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Inspected every input and select in the Add member dialog for a programmatic label, in the live preview.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>Each field is named for assistive technology, and keeps its name once the user has typed into it.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>Every field returns labelled:false -- no for/id pairing, no wrapping label, no aria-label. The visible 'Role' and 'Reporting Manager (for leave approvals)' text is rendered as a bare label element with no for attribute.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The form was built with placeholders standing in for labels, and the two later fields got visual labels that were never wired to their inputs.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1868,42 +1868,42 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1997,32 +1997,32 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -2032,42 +2032,42 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>Each control in a dialog is distinguishable by name.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2114,42 +2114,42 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Visual / alignment</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2161,87 +2161,169 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="82" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P20"/>
+  <autoFilter ref="A1:P21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2252,7 +2334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5906,17 +5988,17 @@
     <row r="75" ht="82" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-224</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add member - all fields</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5931,40 +6013,44 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>Every form field is programmatically labelled</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>All six report labelled:false; four are placeholder-only so the name vanishes on typing, and the two visible labels are not associated</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>TM-06</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="82" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-225</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add member dialog</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5974,45 +6060,49 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>The primary action is reachable without hunting</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+          <t>Submit is 66x44px, position:static, at the end of 2.17 screens of scroll</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>ASK-14</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="82" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-226</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add member - login method</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6022,45 +6112,49 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>The method toggle gates the fields it governs</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
+          <t>'Password login' selected, yet 'Mobile number (for OTP login)' still shows</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ASK-14</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="82" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-227</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add member - menu preview</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6070,17 +6164,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>The form shows what the new member will actually see</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -6090,7 +6184,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>'This member will see these menus' renders the resulting nav live, greying out what is not granted - the strongest part of the form</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -6098,7 +6192,7 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-070</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -6118,17 +6212,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -6138,7 +6232,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -6146,7 +6240,7 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-071</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -6156,27 +6250,27 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -6186,7 +6280,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -6194,17 +6288,17 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-072</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6214,91 +6308,83 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Production sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-073</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>Finance sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-074</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -6308,22 +6394,22 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>No uncaught page errors for any persona</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6338,7 +6424,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
+          <t>0 page errors across owner, sales, production and finance</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -6346,53 +6432,253 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="82" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="82" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="82" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="82" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J84"/>
+  <autoFilter ref="A1:J88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6641,7 +6927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7472,12 +7758,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Rework the Add member form. It is one long scroll of eight controls with no grouping, ending in a fourteen-item permission checklist, and the submit button sits below the fold. Group it into who they are, how they sign in, where they sit, and what they can reach.</t>
+          <t>Rework the Add member form. PLAN, in priority order: (1) give all six fields real associated labels -- see TM-06, worth doing on its own; (2) stop rendering Name and Email in IBM Plex Mono, which reads as an identifier rather than a person -- keep mono for IDs and amounts; (3) make the login-method toggle actually gate its fields, since choosing Password login still shows 'Mobile number (for OTP login)' -- or rename it 'Primary sign-in method' and mark mobile always-optional; (4) put the submit in a sticky footer, because today it is a 66x44px 'Add' at the end of 2.17 screens of scroll; (5) add three section headers for identity, sign-in, and placement; (6) collapse the fourteen-checkbox Access grid behind 'Customise access - n of 14 areas', since Role already sets a sensible default and most additions will not deviate. Together (4) and (6) turn a two-screen form into roughly one screen for the common case. KEEP the 'This member will see these menus' preview exactly as it is.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Founder review. Two concrete problems back it up. First, the first four fields (Name, Email, Temp password, Mobile number) use placeholders INSTEAD of labels, so the moment you type the field name disappears -- while Role and Reporting Manager directly below them do have real labels, so the form is inconsistent with itself. Second, access is chosen from a flat list of fourteen checkboxes at the bottom of a scrolling dialog, which is the densest part of the form and the least explained.</t>
+          <t>Founder review, then measured in the live preview. Dialog is 512x538 with 1163px of content -- 2.17 screens of scroll. All six fields report labelled:false. Name and Email render in IBM Plex Mono 16px. Password and mobile fields are both visible at once despite the method toggle. Submit is 66x44px, position:static, at the very bottom. The one thing that is genuinely strong is the menu preview: it turns fourteen abstract permissions into what the person will actually see on login, greying out what they will not get. That is rare and should survive the redesign.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7587,7 +7873,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Founder idea, marked 'if needed'. The data already exists: members carry reporting_manager_id and a role, and the profile dialog already resolves and displays 'REPORTS TO'. It also answers TM-03, where the page promises REPORTING LINES and the roster never shows them. Worth noting before building: only 1 of 12 members currently has a reporting manager set, so a chart drawn today would be one line and eleven orphans -- the chart is only as good as the reporting data behind it, and that needs filling first.</t>
+          <t>Founder idea, marked 'if needed'. The data already exists: members carry reporting_manager_id and a role, and the profile dialog already resolves and displays 'REPORTS TO'. It also answers TM-03, where the page promises REPORTING LINES and the roster never shows them. Worth noting before building: only 1 of 12 members currently has a reporting manager set, so a chart drawn today would be one line and eleven orphans -- the chart is only as good as the reporting data behind it. SEQUENCING: do ASK-17 first. Putting the reporting line on every card is what makes its absence visible and creates the pressure to fill it in; once most members have a manager, the chart draws itself. Building the chart first would just render the gap at a larger size.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7609,50 +7895,54 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Show the team data that actually answers a question</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Rework what a member card carries. THREE CHANGES. (1) Replace the status pill: every one of the twelve members reads 'Active', including six placeholder accounts that have never signed in, so the field distinguishes nobody. accepted_at and invited_at are both on the record -- show 'Joined 17 Aug' or 'Invited - not yet signed in', which is the question an owner actually has. (2) Put the reporting line where the permission count is: '6 permissions' is a number nobody can act on, and per ASK-13 access should not be on the roster at all, while the page header promises REPORTING LINES and never delivers them. (3) Surface the invite blocker: only 4 of 12 members have a phone, and for the other 8 the Get invite link button simply does not render with no explanation -- say 'No mobile - cannot send invite' on the card so the owner can fix it.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>The API already returns fourteen fields per member and the card uses four of them, two of which say nothing. reporting_manager_id, phone, passwordless, invited_at and accepted_at are all available and all unused. Also worth revisiting the grouping: twelve people across five roles gives five sections, several holding a single card, with the Owner row leaving two thirds of its width empty (TM-02). Under about thirty people a single sorted list with the role as a chip would scan better; group by department once the org chart exists.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>pages/Team.js:411 (accessLabel), :417-450 (card), :475 (manager already resolved); the user record carries invited_at, accepted_at, phone, passwordless</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ASK-13, TM-02, TM-03</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -7662,7 +7952,7 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -7677,7 +7967,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7685,24 +7975,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -7715,7 +8005,7 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7725,12 +8015,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7745,17 +8035,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -7768,7 +8058,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7778,12 +8068,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -7798,17 +8088,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -7821,7 +8111,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -7836,7 +8126,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -7851,17 +8141,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -7874,7 +8164,7 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7884,12 +8174,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -7897,24 +8187,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -7927,7 +8217,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7942,7 +8232,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7957,17 +8247,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -7980,7 +8270,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7990,12 +8280,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8010,17 +8300,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -8033,7 +8323,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -8048,7 +8338,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8063,17 +8353,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -8086,7 +8376,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -8096,12 +8386,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8116,17 +8406,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -8139,7 +8429,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -8149,12 +8439,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8162,24 +8452,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -8192,7 +8482,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -8207,7 +8497,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8215,24 +8505,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -8245,7 +8535,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8260,7 +8550,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8275,17 +8565,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -8298,7 +8588,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -8308,12 +8598,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8321,24 +8611,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -8351,7 +8641,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8361,12 +8651,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8374,24 +8664,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -8404,7 +8694,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -8414,12 +8704,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -8434,17 +8724,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -8457,7 +8747,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8472,7 +8762,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8487,17 +8777,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -8510,7 +8800,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -8520,12 +8810,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -8540,17 +8830,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -8563,58 +8853,164 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="82" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="82" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9562,7 +9958,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>83 (62 pass, 20 fail, 0 blocked, 1 not run)</t>
+          <t>87 (63 pass, 23 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9970,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 5 Medium, 3 Low, 6 Nit</t>
+          <t>1 Critical, 4 High, 6 Medium, 3 Low, 6 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1833,17 +1833,17 @@
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1856,9 +1856,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1868,42 +1868,42 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Compared the desktop scope chips with their mobile counterparts, and confirmed the filtering itself works.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>The selected scope is exposed to assistive technology on both viewports.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>crm-scope-customers and crm-scope-suppliers both report aria-pressed=None; crm-scope-mobile-customers reports 'true' and crm-scope-mobile-suppliers 'false'.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The desktop chip row was built separately from the mobile segmented control and did not carry the ARIA across.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1915,17 +1915,17 @@
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Opened Add customer and inspected every field for a programmatic label.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>Each field is named for assistive technology and keeps its name after the user types.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>All six fields report labelled:false and the dialog's label count is zero. Four of the six also carry no data-testid, which makes them hard to assert on.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>Placeholders are being used as labels throughout the app's forms.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1997,22 +1997,22 @@
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2032,42 +2032,42 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Redundancy</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Listed the buttons in the Add contact dialog.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>One way to back out of the dialog.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Dialog buttons: Customer, Dealer, Supplier, More details, Cancel, Add contact, Close.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>A footer Cancel was added while the dialog primitive still renders its own close control.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2079,17 +2079,17 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2102,9 +2102,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2114,42 +2114,42 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2161,27 +2161,27 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2196,42 +2196,42 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2243,87 +2243,333 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="82" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="82" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="82" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P21"/>
+  <autoFilter ref="A1:P24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2334,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6192,12 +6438,12 @@
     <row r="79" ht="82" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-300</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6217,12 +6463,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>/crm loads directly with the contact list</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -6232,7 +6478,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>11 buyer cards; no redirect</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -6240,12 +6486,12 @@
     <row r="80" ht="82" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-301</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6255,22 +6501,22 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>/crm loads and reflows to a single column</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -6280,7 +6526,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>207 visible elements, 22 interactive</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -6288,37 +6534,37 @@
     <row r="81" ht="82" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-302</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>No horizontal overflow on either viewport</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6328,7 +6574,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>desktop 1440=1440, mobile 390=390</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -6336,37 +6582,37 @@
     <row r="82" ht="82" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-303</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Every control meets the 24px tap-target minimum</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -6376,7 +6622,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>0 under 24px</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -6384,37 +6630,37 @@
     <row r="83" ht="82" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>All text</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>All interactive text meets 4.5:1 contrast</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -6424,7 +6670,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>0 below 4.5:1 on either viewport</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -6432,17 +6678,17 @@
     <row r="84" ht="82" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-305</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>All controls</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6457,12 +6703,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Every button and link has an accessible name</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -6472,7 +6718,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>0 unnamed; 0 images missing alt</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -6480,17 +6726,17 @@
     <row r="85" ht="82" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-306</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -6505,44 +6751,40 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>17 pressed incl. dialogs descended into; 0 crashes</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="82" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-307</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -6557,49 +6799,45 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>Every control can be pressed without crashing the app</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>13 pressed incl. dialogs; 0 crashes</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="82" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-308</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Scope chips</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -6609,12 +6847,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Buyers / Suppliers filter the list correctly</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -6624,7 +6862,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
+          <t>Buyers 11, Suppliers 6, back to Buyers 11</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -6632,53 +6870,889 @@
     <row r="88" ht="82" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>T-309</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Scope chips</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>The selected scope is exposed to assistive technology</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Desktop chips have no aria-pressed; the mobile twins set it</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>CR-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="82" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>T-310</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Add customer opens a complete contact form</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Type segmented control, name, company, phone, email, lifecycle, and a 'More details' disclosure for GSTIN</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="82" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>T-311</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>The form fits without scrolling</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>576x541 with 539px of content - no scroll, unlike Team's 2.17 screens</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="82" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>T-312</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Add contact validation</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>An empty form is refused with a clear reason</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>No API call; dialog stayed open; 'Name is required'</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="82" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>T-313</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Every field is programmatically labelled</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Zero label elements in the dialog; all six fields placeholder-only</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>CR-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="82" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>T-314</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>One way to dismiss the dialog</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Redundancy</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Both a 'Cancel' button and a separate 'Close' X</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="82" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>T-315</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Contact profile route</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>A contact card opens that contact's profile page</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>crm-card-&lt;id&gt; navigates to /contacts/&lt;id&gt;; page renders, no errors</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="82" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>T-316</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>No application errors and no failing API calls</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96" ht="82" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="82" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" ht="82" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="82" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="82" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="82" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="82" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="82" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="82" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="82" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="H105" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J88"/>
+  <autoFilter ref="A1:J105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6927,7 +8001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7758,7 +8832,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Rework the Add member form. PLAN, in priority order: (1) give all six fields real associated labels -- see TM-06, worth doing on its own; (2) stop rendering Name and Email in IBM Plex Mono, which reads as an identifier rather than a person -- keep mono for IDs and amounts; (3) make the login-method toggle actually gate its fields, since choosing Password login still shows 'Mobile number (for OTP login)' -- or rename it 'Primary sign-in method' and mark mobile always-optional; (4) put the submit in a sticky footer, because today it is a 66x44px 'Add' at the end of 2.17 screens of scroll; (5) add three section headers for identity, sign-in, and placement; (6) collapse the fourteen-checkbox Access grid behind 'Customise access - n of 14 areas', since Role already sets a sensible default and most additions will not deviate. Together (4) and (6) turn a two-screen form into roughly one screen for the common case. KEEP the 'This member will see these menus' preview exactly as it is.</t>
+          <t>Rework the Add member form. PLAN, in priority order: (1) give all six fields real associated labels -- see TM-06, worth doing on its own; (2) stop rendering Name and Email in IBM Plex Mono, which reads as an identifier rather than a person -- keep mono for IDs and amounts; (3) make the login-method toggle actually gate its fields, since choosing Password login still shows 'Mobile number (for OTP login)' -- or rename it 'Primary sign-in method' and mark mobile always-optional; (4) put the submit in a sticky footer, because today it is a 66x44px 'Add' at the end of 2.17 screens of scroll; (5) add three section headers for identity, sign-in, and placement; (6) collapse the fourteen-checkbox Access grid behind 'Customise access - n of 14 areas', since Role already sets a sensible default and most additions will not deviate. Together (4) and (6) turn a two-screen form into roughly one screen for the common case. KEEP the 'This member will see these menus' preview exactly as it is. MODEL TO COPY: CRM's own Add contact dialog already does most of this right -- it fits one screen with no scrolling at all, uses the body face rather than mono, and hides GSTIN and the rest behind a 'More details' disclosure. Team's Add member should look like that dialog, not the other way round.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8535,7 +9609,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8545,12 +9619,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8558,24 +9632,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -8588,7 +9662,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -8598,12 +9672,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8618,17 +9692,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -8641,7 +9715,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -8651,12 +9725,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8671,17 +9745,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -8694,7 +9768,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -8704,12 +9778,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -8717,24 +9791,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -8747,7 +9821,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -8757,12 +9831,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -8770,24 +9844,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -8800,7 +9874,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -8810,12 +9884,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -8830,17 +9904,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -8853,7 +9927,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -8863,12 +9937,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -8883,17 +9957,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -8906,7 +9980,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -8916,12 +9990,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -8936,17 +10010,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -8959,58 +10033,217 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="82" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="82" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="82" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9958,7 +11191,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>87 (63 pass, 23 fail, 0 blocked, 1 not run)</t>
+          <t>104 (77 pass, 26 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -9970,7 +11203,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 6 Medium, 3 Low, 6 Nit</t>
+          <t>1 Critical, 4 High, 7 Medium, 4 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2079,32 +2079,32 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2114,42 +2114,42 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Responsive / layout</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Tapped the + button in the CRM header on a 375px phone and measured where the menu it opens actually lands.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>The menu opens inside the screen with its options readable.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>Viewport 375px; the menu spans x=315 to x=615, width 300px, overflowing the right edge by 240px -- 80 per cent clipped. Each item is 290px wide starting at x=320, leaving 55px visible.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The menu is right-anchored to its trigger with a fixed 300px width and no collision handling, which is fine beside a desktop toolbar and wrong beside a button that already sits at the right edge of a phone.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2161,32 +2161,32 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2196,42 +2196,42 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Dead control</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Tapped the Filter control in the CRM header on a 375px phone and compared the page before and after.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>It reveals the status and sort controls, which desktop shows inline.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Before and after the tap: body text 746 chars both times, 356 elements both times, 0 dialogs, 0 menus, 0 sheets. crm-status-filter and crm-sort are present but measure 0x0.</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>The control was given an icon and an aria-label but never wired to the state that reveals the filter row.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2243,32 +2243,32 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2278,42 +2278,42 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Responsive / layout</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Measured the card grid and every text node inside it at 375px.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>On a phone a contact list is readable, and a customer's name is not cut off.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>grid-template-columns resolves to '160.5px 160.5px' at a 375px viewport; 8 leaf text nodes have scrollWidth greater than clientWidth.</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The grid keeps two columns below the breakpoint where the content stops fitting.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2360,42 +2360,42 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Design system</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Measured the colour of every primary button on the contact profile page and compared it with primaries elsewhere in the app.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>One primary colour across the product.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Log button background rgb(55,58,205) with white text; the app's primaries elsewhere measure rgb(12,12,13).</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>An indigo accent from a different design direction survived on this screen when the rest of the app settled on ink.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2407,17 +2407,17 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2442,42 +2442,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2489,87 +2489,415 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="82" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="82" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="82" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="82" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2580,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7266,22 +7594,22 @@
     <row r="96" ht="82" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-317</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Scope chips</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7291,12 +7619,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>Switching to Suppliers reloads the list</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
@@ -7306,7 +7634,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>Buyers 11 -&gt; Suppliers 6, correct records, chip state flips</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -7314,37 +7642,37 @@
     <row r="97" ht="82" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-318</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Sort control</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>Sorting by outstanding puts the biggest debtor first</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
@@ -7354,7 +7682,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>Krishna Garments Rs 4,00,000 first, then Nashik Traders Rs 64,000</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -7362,37 +7690,37 @@
     <row r="98" ht="82" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-319</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add contact menu</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>The menu opens with its three options readable</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
@@ -7402,7 +7730,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>aria-expanded flips, role=menu appears: New Buyer, New Supplier, Import</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -7410,85 +7738,89 @@
     <row r="99" ht="82" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-320</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Add contact menu</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>The menu opens inside the screen</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr"/>
+          <t>80% clipped off the right edge; only a 55px strip of icons is visible</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>CR-04</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="82" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-321</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>New customer dialog</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>The form is grouped and fits one screen</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
@@ -7498,7 +7830,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>Sections Type / Identity / Contact / Classification, required marked, More details disclosure, Cancel beside Add contact, no scrolling</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -7506,22 +7838,22 @@
     <row r="101" ht="82" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-322</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Filter control</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7531,60 +7863,64 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Filter reveals the status and sort controls</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr"/>
+          <t>Completely inert; status filter and sort exist at 0x0 so neither is reachable on a phone</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>CR-05</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="82" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-323</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Contact cards</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Customer names are readable on a phone</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -7594,34 +7930,34 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
+          <t>Two-column grid at 160.5px per card truncates 8 text nodes including names</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>CR-06</t>
         </is>
       </c>
     </row>
     <row r="103" ht="82" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-324</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Contact profile</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -7631,128 +7967,616 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>A contact card opens a profile with money and activity</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>Outstanding / Total Billed / Total Paid / Open Complaints tiles, AI scoring, and inline activity logging</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="82" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-325</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Contact profile</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Primary actions use the app's primary colour</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H104" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr"/>
+          <t>Log button is indigo rgb(55,58,205); the app's primaries are rgb(12,12,13)</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>CR-07</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="82" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>T-326</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Mobile header controls</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Header controls meet the 44px touch guideline</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Filter 44x44, Add contact 44x44, scope segment 166x44, bell 48x48</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="82" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="82" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="82" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="82" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" ht="82" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="82" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112" ht="82" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="82" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="82" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="82" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8001,7 +8825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9291,7 +10115,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9301,12 +10125,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -9314,24 +10138,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -9344,7 +10168,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -9354,12 +10178,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -9367,24 +10191,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -9397,7 +10221,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -9407,12 +10231,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -9427,17 +10251,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -9450,7 +10274,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -9460,12 +10284,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -9480,17 +10304,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -9503,7 +10327,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9513,12 +10337,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -9533,17 +10357,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -9556,7 +10380,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -9566,12 +10390,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9586,17 +10410,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -9609,7 +10433,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -9619,12 +10443,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9639,17 +10463,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -9662,7 +10486,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -9672,12 +10496,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9685,24 +10509,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -9715,7 +10539,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -9725,12 +10549,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9738,24 +10562,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -9768,7 +10592,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -9783,7 +10607,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9791,24 +10615,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -9821,7 +10645,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -9836,7 +10660,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9851,17 +10675,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -9874,7 +10698,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -9884,12 +10708,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9897,24 +10721,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -9927,7 +10751,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -9942,7 +10766,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9950,24 +10774,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -9980,7 +10804,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -9990,12 +10814,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -10003,24 +10827,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -10033,7 +10857,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10043,12 +10867,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10056,24 +10880,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -10086,7 +10910,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -10096,12 +10920,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -10116,17 +10940,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -10139,7 +10963,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10149,12 +10973,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10169,17 +10993,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -10192,58 +11016,270 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="82" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="82" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="82" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="82" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11191,7 +12227,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>104 (77 pass, 26 fail, 0 blocked, 1 not run)</t>
+          <t>114 (83 pass, 30 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -11203,7 +12239,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 4 High, 7 Medium, 4 Low, 7 Nit</t>
+          <t>1 Critical, 6 High, 8 Medium, 5 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2407,22 +2407,22 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2430,9 +2430,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2442,42 +2442,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Data leak to UI</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Read the 'In progress' accordion on a contact profile where some pending deliveries have no due date.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>A missing due date is either omitted or says something a person can read.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>ContactProfileMobile.jsx:215 renders {humanDate(d.due_date) || `Due ${d.due_date}`}. humanDate is dueLabel(iso)?.text || null, so a missing date returns null and the fallback interpolates the undefined value straight into the string.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The fallback was written for a date the humaniser cannot PARSE, but it also catches a date that is simply ABSENT, and prints it.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2524,42 +2524,42 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Visual / layout</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Measured the grid that renders each role group on the team roster.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2606,42 +2606,42 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Information design</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2653,32 +2653,32 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Member profile dialog</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2688,42 +2688,42 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>Each control in a dialog is distinguishable by name.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2770,42 +2770,42 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Visual / alignment</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2817,87 +2817,169 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="82" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P28"/>
+  <autoFilter ref="A1:P29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2908,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8090,103 +8172,111 @@
     <row r="106" ht="82" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-327</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Contact profile - In progress</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>A missing due date does not print raw values to the user</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H106" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr"/>
+          <t>Rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>CR-08</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="82" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-328</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Contact profile - In progress</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>The list distinguishes workflows from deliveries and rows are actionable</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr"/>
+          <t>Two entity types share identical styling; titles repeat as bare 'sale'; a 'Delivered' row sits under 'In progress'; no row is tappable</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>ASK-18</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="82" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-070</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -8206,12 +8296,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -8226,7 +8316,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -8234,7 +8324,7 @@
     <row r="109" ht="82" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-071</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -8254,12 +8344,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8274,7 +8364,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -8282,7 +8372,7 @@
     <row r="110" ht="82" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-072</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -8302,17 +8392,17 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Production sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
@@ -8322,7 +8412,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -8330,7 +8420,7 @@
     <row r="111" ht="82" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-073</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -8340,27 +8430,27 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Finance sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
@@ -8370,7 +8460,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -8378,17 +8468,17 @@
     <row r="112" ht="82" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-074</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8398,54 +8488,50 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>No uncaught page errors for any persona</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="82" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-080</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Console + network</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8455,49 +8541,45 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>No application console errors and no failing API calls in normal use</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
     </row>
     <row r="114" ht="82" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-081</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Global search dialog</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8507,76 +8589,180 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>Opening global search logs no accessibility errors</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr"/>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="82" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="82" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117" ht="82" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H115" s="9" t="inlineStr">
+      <c r="H117" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
+  <autoFilter ref="A1:J117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8825,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9850,50 +10036,54 @@
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-18</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Iterate the 'In progress' / task listing</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>Rework the In progress list on the contact profile. FIVE THINGS. (1) Fix the 'Due undefined' leak first -- that is CR-08 and it is visible to customers. (2) The list silently mixes two different kinds of thing: workflows, whose second line is a STAGE ('Delivered', 'In transit', 'Ordered'), and pending deliveries, whose second line is a DATE AND AMOUNT. They share identical typography with nothing separating them, so the reader has to infer which is which from the shape of the text. Split them into labelled groups, or give each row a type marker. (3) Titles are not doing their job -- three rows read simply 'sale', which identifies nothing when there are three of them; fall back to something distinguishing (the order, the amount, the date) rather than the bare record type. (4) A row showing stage 'Delivered' sits under a heading that says In progress, which contradicts itself -- either exclude terminal stages or rename the group to something like 'Open with them'. (5) Nothing in the list is tappable: these are plain list items, so a user who sees an order they care about cannot open it. Make each row navigate to its workflow or delivery.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>Founder review of the In progress card. Everything above is visible in one screenshot of five rows, which is the tell -- a list this short should not have this many ways to confuse. The underlying data is fine; it is the presentation layer that needs the pass.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>pages/mobile/ContactProfileMobile.jsx:199-222 (the In progress accordion)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>CR-08</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>To do</t>
@@ -9903,7 +10093,7 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9918,7 +10108,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -9926,24 +10116,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -9956,7 +10146,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -9966,12 +10156,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -9986,17 +10176,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -10009,7 +10199,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -10019,12 +10209,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -10039,17 +10229,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -10062,7 +10252,7 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -10077,7 +10267,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10092,17 +10282,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -10115,7 +10305,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CR-04</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -10125,12 +10315,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu (mobile)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -10145,17 +10335,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -10168,7 +10358,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CR-05</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -10183,7 +10373,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Filter button (mobile)</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -10198,17 +10388,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -10221,7 +10411,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10231,12 +10421,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10244,24 +10434,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -10274,7 +10464,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -10289,7 +10479,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -10304,17 +10494,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -10327,7 +10517,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10337,12 +10527,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10357,17 +10547,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -10380,7 +10570,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -10395,7 +10585,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -10410,17 +10600,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -10433,7 +10623,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10443,12 +10633,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10463,17 +10653,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -10486,7 +10676,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -10501,7 +10691,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -10516,17 +10706,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -10539,7 +10729,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10549,12 +10739,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10569,17 +10759,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -10592,7 +10782,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -10607,7 +10797,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -10622,17 +10812,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -10645,7 +10835,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10655,12 +10845,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10668,24 +10858,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -10698,7 +10888,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -10708,12 +10898,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -10721,24 +10911,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -10751,7 +10941,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10761,12 +10951,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10781,17 +10971,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -10804,7 +10994,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -10814,12 +11004,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -10834,17 +11024,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -10857,7 +11047,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10867,12 +11057,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10887,17 +11077,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -10910,7 +11100,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -10920,12 +11110,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -10933,24 +11123,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -10963,7 +11153,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -10973,12 +11163,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -10986,24 +11176,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -11016,7 +11206,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -11026,12 +11216,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -11046,17 +11236,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -11069,7 +11259,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>CR-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -11079,12 +11269,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Add contact dialog - dismiss controls</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -11099,17 +11289,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -11122,7 +11312,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -11137,7 +11327,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Owner section grid</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -11152,17 +11342,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -11175,7 +11365,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -11185,12 +11375,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Member cards</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -11205,17 +11395,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -11228,58 +11418,164 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="82" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="82" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
+  <autoFilter ref="A1:K47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12227,7 +12523,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>114 (83 pass, 30 fail, 0 blocked, 1 not run)</t>
+          <t>116 (83 pass, 32 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12535,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 6 High, 8 Medium, 5 Low, 7 Nit</t>
+          <t>1 Critical, 6 High, 9 Medium, 5 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$47</definedName>
@@ -113,12 +113,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE7E7"/>
+        <fgColor rgb="00E8F3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F3EC"/>
+        <fgColor rgb="00FDE7E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,13 +174,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,7 @@
     <col width="62" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="58" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -681,6 +682,11 @@
           <t>Found on</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -715,7 +721,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -761,6 +767,11 @@
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: Update / Escalate opens the form; app stays alive; 0 CTRL_ON errors.</t>
         </is>
       </c>
     </row>
@@ -797,7 +808,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -843,6 +854,11 @@
       <c r="P3" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: mobile 'Log update or hand off' now opens the update form.</t>
         </is>
       </c>
     </row>
@@ -879,7 +895,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -925,6 +941,11 @@
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: frontend/src/components/ErrorBoundary.jsx exists.</t>
         </is>
       </c>
     </row>
@@ -961,7 +982,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1007,6 +1028,11 @@
       <c r="P5" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: status change now reflects on the card without a reload (set 'waiting', card read 'waiting').</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1069,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1089,6 +1115,11 @@
       <c r="P6" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: overflow menu &gt; View details opens task-detail-&lt;id&gt; with Delete visible.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1156,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1171,6 +1202,11 @@
       <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: global search dialog's aria-labelledby now resolves to 'Search'; 0 Radix warnings.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1243,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1253,6 +1289,11 @@
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: Dex FAB scrim present after opening, gone after Escape.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1330,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1335,6 +1376,11 @@
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: no task-only controls visible in the Leave view.</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1415,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1419,6 +1465,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="82" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1446,14 +1493,14 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1499,6 +1546,11 @@
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: delete controls now named per card, e.g. 'Delete card: Toyota Order Dispatch'.</t>
         </is>
       </c>
     </row>
@@ -1528,14 +1580,14 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1581,6 +1633,11 @@
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: headings read ['My Work', 'Leave'] in the Leave view.</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1667,12 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1665,6 +1722,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1697,7 +1755,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1747,6 +1805,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1779,7 +1838,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1829,6 +1888,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="82" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1856,12 +1916,12 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1911,6 +1971,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="82" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1943,7 +2004,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1993,6 +2054,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="82" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2020,12 +2082,12 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2075,6 +2137,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2107,7 +2170,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2157,6 +2220,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2189,7 +2253,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2239,6 +2303,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2271,7 +2336,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2321,6 +2386,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2348,12 +2414,12 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2403,6 +2469,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2435,7 +2502,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2485,6 +2552,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2512,12 +2580,12 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2567,6 +2635,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2594,12 +2663,12 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2649,6 +2718,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2676,12 +2746,12 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2731,6 +2801,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2758,14 +2829,14 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2811,6 +2882,11 @@
       <c r="P27" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
         </is>
       </c>
     </row>
@@ -2840,14 +2916,14 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2893,6 +2969,11 @@
       <c r="P28" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
         </is>
       </c>
     </row>
@@ -2922,12 +3003,12 @@
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
@@ -2977,9 +3058,10 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="Q29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P29"/>
+  <autoFilter ref="A1:Q29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3093,7 +3175,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3141,7 +3223,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3189,7 +3271,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3237,7 +3319,7 @@
           <t>Visual</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3285,7 +3367,7 @@
           <t>Visual</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3337,7 +3419,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3385,7 +3467,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3433,7 +3515,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3481,7 +3563,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3529,7 +3611,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3577,7 +3659,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3625,7 +3707,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3673,7 +3755,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3721,7 +3803,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3769,7 +3851,7 @@
           <t>Visual</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3821,7 +3903,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3869,7 +3951,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3917,7 +3999,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3969,7 +4051,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4021,7 +4103,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4069,7 +4151,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4121,7 +4203,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4173,7 +4255,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4225,7 +4307,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4277,7 +4359,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4325,7 +4407,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4373,7 +4455,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4425,7 +4507,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4477,7 +4559,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4525,7 +4607,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4577,7 +4659,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4625,7 +4707,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4673,7 +4755,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4721,7 +4803,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4769,7 +4851,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4817,7 +4899,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4865,7 +4947,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4913,7 +4995,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4961,7 +5043,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5009,7 +5091,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5057,7 +5139,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5105,7 +5187,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5157,7 +5239,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5205,7 +5287,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5253,7 +5335,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5301,7 +5383,7 @@
           <t>Information architecture</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5353,7 +5435,7 @@
           <t>Information architecture</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5405,7 +5487,7 @@
           <t>Orientation</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5457,7 +5539,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5505,7 +5587,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5553,7 +5635,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5601,7 +5683,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5649,7 +5731,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5697,7 +5779,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5745,7 +5827,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5793,7 +5875,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5841,7 +5923,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5889,7 +5971,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5937,7 +6019,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5985,7 +6067,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6033,7 +6115,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6085,7 +6167,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6133,7 +6215,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6181,7 +6263,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6233,7 +6315,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H66" s="9" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6281,7 +6363,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6377,7 +6459,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6425,7 +6507,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6473,7 +6555,7 @@
           <t>Visual</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6525,7 +6607,7 @@
           <t>Information architecture</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6577,7 +6659,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H73" s="9" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6625,7 +6707,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H74" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6677,7 +6759,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6729,7 +6811,7 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6781,7 +6863,7 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6833,7 +6915,7 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6881,7 +6963,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6929,7 +7011,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6977,7 +7059,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7025,7 +7107,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7073,7 +7155,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7121,7 +7203,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7169,7 +7251,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7217,7 +7299,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H86" s="9" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7265,7 +7347,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7313,7 +7395,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7365,7 +7447,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H89" s="9" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7413,7 +7495,7 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7461,7 +7543,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7509,7 +7591,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7561,7 +7643,7 @@
           <t>Redundancy</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7613,7 +7695,7 @@
           <t>Routing</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7661,7 +7743,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H95" s="9" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7709,7 +7791,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H96" s="9" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7757,7 +7839,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7805,7 +7887,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H98" s="9" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7853,7 +7935,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -7905,7 +7987,7 @@
           <t>Usability</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7953,7 +8035,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8005,7 +8087,7 @@
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8057,7 +8139,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H103" s="9" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8105,7 +8187,7 @@
           <t>Design system</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8157,7 +8239,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8205,7 +8287,7 @@
           <t>Data quality</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8257,7 +8339,7 @@
           <t>Information design</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8309,7 +8391,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H108" s="9" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8357,7 +8439,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H109" s="9" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8405,7 +8487,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H110" s="9" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8453,7 +8535,7 @@
           <t>Permissions</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8501,7 +8583,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H112" s="9" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8549,7 +8631,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H113" s="9" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8597,7 +8679,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8649,7 +8731,7 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="H115" s="4" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -8701,7 +8783,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H116" s="9" t="inlineStr">
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8749,7 +8831,7 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="H117" s="9" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9131,7 +9213,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9186,7 +9268,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9325,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9378,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9408,7 @@
           <t>Future scope</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9408,7 +9490,7 @@
           <t>MW-11, MW-12</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9465,7 +9547,7 @@
           <t>ASK-6</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9579,7 +9661,7 @@
           <t>MW-01, MW-08, MW-09</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9634,7 +9716,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9771,7 @@
           <t>ASK-9</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9746,7 +9828,7 @@
           <t>ASK-9</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9803,7 +9885,7 @@
           <t>TM-05</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9856,7 +9938,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9913,7 +9995,7 @@
           <t>ASK-13</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9945,7 +10027,7 @@
           <t>Future scope</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10027,7 +10109,7 @@
           <t>ASK-13, TM-02, TM-03</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10084,7 +10166,7 @@
           <t>CR-08</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10137,7 +10219,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10190,7 +10272,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10243,7 +10325,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10296,7 +10378,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10349,7 +10431,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10402,7 +10484,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10455,7 +10537,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10508,7 +10590,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10561,7 +10643,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10614,7 +10696,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10667,7 +10749,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10720,7 +10802,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10773,7 +10855,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10826,7 +10908,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10879,7 +10961,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10932,7 +11014,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -10964,7 +11046,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10985,7 +11067,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11017,7 +11099,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11038,7 +11120,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11070,7 +11152,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11091,7 +11173,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11123,7 +11205,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11144,7 +11226,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11176,7 +11258,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11197,7 +11279,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11229,7 +11311,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11250,7 +11332,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11282,7 +11364,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11303,7 +11385,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11335,7 +11417,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11356,7 +11438,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11388,7 +11470,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11409,7 +11491,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11441,7 +11523,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11462,7 +11544,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11494,7 +11576,7 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11515,7 +11597,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11547,7 +11629,7 @@
           <t>By design</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
@@ -11568,7 +11650,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2557,32 +2557,32 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2592,47 +2592,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Read the panel's own caption, then checked the service that produces the numbers underneath it.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>A page that states a time window applies it.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>services/operating_score.py contains no created_at, no timedelta, no days= and no since; the only match for '30' is .to_list(3000). Live data spans 2026-08-08 to 2026-09-09 and all of it is counted.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>The caption was written for an intended windowed metric that was never implemented, or was implemented and later dropped.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2640,32 +2640,32 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>'Do these first' on mobile</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2675,47 +2675,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Responsive / layout</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Measured the page's primary call to action against the fixed dark band beneath it on a 375x812 phone.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>The list of what to do first is readable on a phone.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Band: position fixed, z-index 20, top 454, height 374 of an 812px viewport. Overlap with 'Do these first' measured at 256px. Document scrollHeight 812 = clientHeight 812.</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>A section styled as a full-bleed dark band on desktop keeps position fixed at mobile widths, where there is not room for both it and the content above it.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -2723,17 +2723,17 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2746,9 +2746,9 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2758,47 +2758,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Recomputed all four legs from the raw records and compared with the API.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A score meant to guide the next action responds when that action is taken.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>API: overall 19, execution 0, finance 57, sales 22, responsiveness 0. Recomputed from 148 tasks: done 11, open 130, overdue 68, completion 0.078; execution = clamp(7.8 - 20.9) = 0. Responsiveness = clamp(100-192-204) = 0.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>Both legs subtract unbounded absolute penalties from 100 and then clamp at zero, so any moderately messy workspace saturates.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -2806,109 +2806,105 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Read what the Sales leg is computed from.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A category called Sales reflects selling.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>_score_sales(decisions) = approved/total*100. API Sales = 22 with total_decisions 77, approved 17.</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>The leg was named for the business area it was meant to represent rather than the quantity actually available to compute.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2916,152 +2912,903 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Traced where a single overdue task lands in the model.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>Each fact is counted once.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>_score_execution applies overdue_ratio*40; the responsiveness expression applies overdue*3.</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The two legs were designed independently and both reached for the same signal.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>OP-06</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Operating score model</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Checked how the penalties behave as a business grows.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>The same performance scores the same at any size.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>responsiveness = 100 - open_complaints*12 - overdue*3; finance = collected*100 - overdue_inv*5.</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Fixed point-costs were chosen against an assumed small tenant.</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>services/operating_score.py:_company_operating_view</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="82" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>OP-07</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Operating score - empty workspace</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Read what each leg returns when its denominator is zero.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>A workspace with no data reads as unknown, not as a grade.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>completion, approved_rate and collected all default to 0.7; enough_data = actionable &gt;= 3 or inv_count &gt; 0.</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>A neutral default was chosen so an empty tenant would not look alarming.</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="82" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>OP-08</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Category cards</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Looked at how a zero-scoring category is drawn.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>A bad score and a missing score look different.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Desktop screenshot: Execution 0/100 and Responsiveness 0/100 with unfilled tracks, beside Finance 57 and Sales 22 with filled ones.</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>The bar encodes only the value, and zero has no visual form.</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>pages/OperatingScore.js (category card progress track)</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="82" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>OP-09</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>'View all' links and the formula panel (mobile)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Responsive / accessibility</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Measured every remaining mobile control on the Ops page.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Links are big enough to tap, unobstructed, and the whole page is reachable.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>View all: 61x20 at y=751, elementFromPoint returns dex-fab; second at y=947, outside the viewport. operating-formula-toggle: 223x44 at y=1153, inViewport false, and the automated sweep could not click it.</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>The same fixed-band layout as OP-02: the document does not scroll, so anything below the fold is unreachable rather than merely below.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="82" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Visual / layout</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Measured the grid that renders each role group on the team roster.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="82" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="82" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="82" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="82" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="82" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q29"/>
+  <autoFilter ref="A1:Q38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3072,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8358,12 +9105,12 @@
     <row r="108" ht="82" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-400</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8383,12 +9130,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>/operating-score loads with the score and all four categories</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8398,7 +9145,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>Overall 19/100, four category cards, next-moves, quick stats</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -8406,12 +9153,12 @@
     <row r="109" ht="82" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-401</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8421,22 +9168,22 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>/operating-score loads and reflows</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8446,7 +9193,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>317 visible elements, compact Key scores card</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -8454,37 +9201,37 @@
     <row r="110" ht="82" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-402</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Page shell</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>No horizontal overflow; every control named; images have alt</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8494,7 +9241,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>desktop 1440=1440, mobile 390=390, 0 unnamed</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -8502,37 +9249,37 @@
     <row r="111" ht="82" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Every control pressed without crashing the app</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8542,7 +9289,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>47 checks passed across both viewports; 0 crashes</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -8550,37 +9297,37 @@
     <row r="112" ht="82" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-404</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Category breakdown</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Each category opens a breakdown that states its weight</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8590,7 +9337,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>Execution 35%, Finance 25%, Sales 20%, Responsiveness 20% - the model is disclosed to the user</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
@@ -8598,22 +9345,22 @@
     <row r="113" ht="82" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-405</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Next-move actions</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 390x844</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8623,12 +9370,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Each recommended action links somewhere real</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8638,7 +9385,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>ops-action-overdue -&gt; /my-work?filter=overdue; ops-action-complaints -&gt; /crm</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
@@ -8646,22 +9393,22 @@
     <row r="114" ht="82" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-406</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Score arithmetic</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8671,49 +9418,45 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>The reported legs match a recomputation from raw records</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>Recomputed execution 0 and responsiveness 0 from 148 tasks; both match the API exactly - the model is implemented as designed</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
     </row>
     <row r="115" ht="82" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-407</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8723,12 +9466,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>The stated time window is the one applied</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -8738,29 +9481,29 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
+          <t>Caption says 'Last 30 days'; the service applies no date filter at all</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>OP-01</t>
         </is>
       </c>
     </row>
     <row r="116" ht="82" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-408</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>'Do these first'</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8775,76 +9518,1028 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>The primary call to action is readable</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr"/>
+          <t>256 of its 285px sit behind a fixed band; the document cannot scroll</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>OP-02</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="82" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>T-409</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Score responsiveness</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Acting on the advice moves the score</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Responsiveness computes to -296 before clamping; closing all 16 complaints would leave it at 0</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>OP-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="82" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>T-410</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>'Sales' category</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>The category measures what its label says</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>It is approved/total decisions; contains no revenue, orders or pipeline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>OP-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="82" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>T-411</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Score model</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Each underlying fact is counted once</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Overdue tasks are charged to both Execution and Responsiveness</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>OP-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="82" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>T-412</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Score model</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>The score means the same at any company size</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>complaints x12, overdue x3, overdue invoices x5 are absolute, not rates</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>OP-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="82" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>T-413</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Empty workspace</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>A workspace with no data reads as unknown</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Defaults of 0.7 give a brand-new tenant roughly 70/100</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>OP-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="82" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>T-414</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Category cards</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>A floored score looks different from a missing one</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>0/100 with an empty bar is identical to unmeasured</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>OP-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="82" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>T-415</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>'View all' + formula panel</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Links are tappable and the whole page is reachable</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>View all is 61x20 and one is covered by dex-fab; the formula toggle sits at y=1153 on an 812px screen and cannot be reached</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>OP-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="82" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>T-416</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Next-move honesty</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Recommendations do not claim unearned outcomes</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>scoreActions deliberately removed hardcoded '+6 pts' lift estimates because the score has no history to fit a counterfactual against</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="82" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>T-417</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Finance leg</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Only inbound payments count as money collected</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>payments query filters direction='in'; outbound supplier payments excluded</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126" ht="82" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>T-418</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Weighting</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Finance-less roles</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Weights renormalise when a leg is unavailable</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>finance is null without the permission and the remaining weights rescale</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" ht="82" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128" ht="82" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="82" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130" ht="82" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131" ht="82" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" ht="82" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" ht="82" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="82" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="82" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" ht="82" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J117"/>
+  <autoFilter ref="A1:J136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9093,7 +10788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10175,50 +11870,54 @@
     <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MW-08</t>
+          <t>ASK-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UI audit</t>
+          <t>Founder review</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Task card - Update / Escalate</t>
+          <t>Rework the operating score around what an SME owner asks</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bug fix</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Product decision</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
+          <t>The four legs answer 'how tidy is the workspace', not 'how is the business doing'. PROPOSED SET, with the reasoning. (1) CASH, heaviest weight: collection rate plus receivables ageing. For an India-first SME this is the question -- am I getting paid -- and half of it already exists as the finance leg. (2) EXECUTION, rewritten as a rate over a window: work completed in the last 30 days against work created, plus the median age of what is still open. The current all-time completion ratio can only fall. (3) CUSTOMER: complaints per active customer and time to first response -- rates, so they survive growth. (4) DECISION VELOCITY: median time from a decision being raised to it being settled, and the share still pending past a threshold. That is the honest name for what the Sales leg already computes, and for a product called a decision OS it may be the most defensible metric on the page. Add a real SALES leg only if wanted -- invoices already carry revenue this period against last. MECHANICS that matter as much as the choice of legs: score every leg as a bounded rate so it always has somewhere to move (OP-03); count lateness once (OP-05); use rates not fixed point-costs so the score means the same at any size (OP-06); apply the rolling window the UI already claims (OP-01); and show 'not enough data yet' instead of a defaulted 70 (OP-07).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
+          <t>Founder asked whether the KPIs are the right ones. Measured against live data the answer is that the model is well built but measuring the wrong things: overall 19 out of 100, with two of the four legs pinned at the floor and giving no feedback, one leg labelled Sales that contains no sales, and a caption promising a 30-day window that is never applied. An owner following the page's own advice to the letter would watch the score not move. Worth saying what is good, because it should survive any rewrite: the weights renormalise correctly when a leg is unavailable, the finance leg correctly counts only inbound payments, the next-move list is derived from real figures, and somebody deliberately removed fabricated '+6 pts' lift estimates because the score has no history to justify them. That is the right instinct, and it is the same instinct that should now drive giving the score a time window so it can have a history at all.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>services/operating_score.py (the whole model); pages/OperatingScore.js (cards, captions, delta chip)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>OP-01, OP-03, OP-04, OP-05, OP-06, OP-07</t>
+        </is>
+      </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
           <t>To do</t>
@@ -10228,7 +11927,7 @@
     <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MW-09</t>
+          <t>MW-08</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -10243,7 +11942,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Task card - 'Log update or hand off' (mobile)</t>
+          <t>Task card - Update / Escalate</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -10251,24 +11950,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
+          <t>Restyle that one button to the segmented-control treatment the rest of the toolbar moved to in the same commit (kr-pressed / kr-pop, as the priority bands use), or simply restore the two constants. Then stop the class recurring: craco narrows ESLint to react-hooks rules only, which drops eslint-config-react-app's no-undef - the rule that would have failed the build on this exact line.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
+          <t>The app CRASHES. A ReferenceError is thrown while rendering the form, the form never appears, and the whole React tree unmounts - the page is gone, not just the form. Recovery needs a reload. The work trail, hand-off and escalation flow is therefore completely unusable.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
+          <t>pages/MyWork.js:147 (UpdateForm); constants removed in 5fb96f2; lint narrowed at craco.config.js:74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -10281,7 +11980,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MW-10</t>
+          <t>MW-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -10291,12 +11990,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application shell</t>
+          <t>Task card - 'Log update or hand off' (mobile)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -10311,17 +12010,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
+          <t>Wire it to the same handler its desktop counterpart uses so it opens UpdateForm - and fix MW-08 first, or the newly working button will simply crash the page instead of doing nothing.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
+          <t>Nothing happens at all - no form, no navigation, no error. The button is inert. Combined with MW-08 on desktop, there is no working way to log a task update or hand a task off on either viewport.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
+          <t>pages/MyWork.js:1496-1505 (log-update-m button, no onClick)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -10334,7 +12033,7 @@
     <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MW-01</t>
+          <t>MW-10</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -10344,12 +12043,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Task card - status control</t>
+          <t>Application shell</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10364,17 +12063,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
+          <t>Add an error boundary around the routed page area - it should show a short apology, a Reload action, and report the error - so a single broken component costs one panel rather than the whole product. Worth a second boundary around the app shell as a backstop.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
+          <t>One component throwing takes down the entire application. After the MW-08 crash the React root is left with no children, so the user is looking at a blank page with no message and no recovery except a manual reload. Any future render error anywhere will behave the same way.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
+          <t>frontend/src/App.js (route tree) and components/Layout.js (shell)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -10387,7 +12086,7 @@
     <row r="24" ht="82" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MW-02</t>
+          <t>MW-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -10402,7 +12101,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Task card - detail dialog</t>
+          <t>Task card - status control</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -10417,17 +12116,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
+          <t>Write the PATCH response straight into the cache instead of trusting the refetch: qc.setQueryData(['tasks', mine], rows =&gt; rows.map(r =&gt; r.id === t.id ? data : r)) using the object the PATCH already returns, then invalidate. That is the standard React Query update-from-response pattern and removes the race entirely. If the refetch must stay authoritative, the list read needs read-your-writes consistency instead.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
+          <t>The save succeeds (PATCH returns 200 with the new status) and a success toast appears, but the card keeps showing the PREVIOUS status. The list refetch that follows returns the pre-change value, which overwrites the UI. The correct status only appears after a full page reload. Reproduced 8 out of 8 attempts; mobile pills stay unpressed the same way. The progress percentage behaves identically: setting 50% stores 50 on the server while the card still reads 0 until reloaded.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
+          <t>pages/MyWork.js:1127 setStatus / 1134 setProgress; refresh() at 2102</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -10440,7 +12139,7 @@
     <row r="25" ht="82" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CR-04</t>
+          <t>MW-02</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -10450,12 +12149,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Add contact menu (mobile)</t>
+          <t>Task card - detail dialog</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -10470,17 +12169,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
+          <t>Give the card a way in: an overflow / more menu on the summary row, or make the title open details, calling setDetailOpen(true). If the detail dialog is genuinely retired, delete the component and move the Delete action onto the inline expanded card instead - either way a task must be deletable.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
+          <t>There is NO delete control anywhere in My Work, on either viewport, and the task detail dialog never opens. The dialog and its Delete button exist in the code but are unreachable, so the proof gallery, the source-reference panel and the AI insight panel are all dead UI too.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
+          <t>pages/MyWork.js:986 (state), 1837 (render), 737-890 (the dialog + delete)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -10493,7 +12192,7 @@
     <row r="26" ht="82" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CR-05</t>
+          <t>CR-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10508,7 +12207,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Filter button (mobile)</t>
+          <t>Add contact menu (mobile)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10523,17 +12222,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
+          <t>Give the popover collision-aware placement so it flips and clamps inside the viewport, or on mobile present the same three choices as a bottom sheet -- the pattern the app already uses elsewhere for phone menus.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
+          <t>Four fifths of the menu is off-screen. It opens anchored to the + button and runs off the right edge, so all the user sees is a 55px strip carrying three anonymous icons -- every label is cut off. 'New Buyer', 'New Supplier' and 'Import from spreadsheet' are all invisible, so adding a contact on a phone means guessing which icon to press.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
+          <t>pages/CRM.js:405-480 (crm-add-menu popover)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -10546,7 +12245,7 @@
     <row r="27" ht="82" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>CR-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -10556,12 +12255,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Filter button (mobile)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -10569,24 +12268,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Wire it to a sheet or popover containing the status filter and sort that desktop shows inline. Both controls already exist and only need somewhere to be shown.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Nothing happens at all. Not a single thing changes -- same text, same element count, no dialog, no menu, no sheet. Meanwhile the status filter and the sort control both exist in the DOM at zero size, so on a phone there is no way to filter by status or change the sort order.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/CRM.js:739 (crm-mobile-filter); the controls it should reveal are at :858 (crm-status-filter) and :869 (crm-sort)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -10599,7 +12298,7 @@
     <row r="28" ht="82" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -10609,12 +12308,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Team execution panel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10622,24 +12321,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Decide which is true and make them agree. A rolling window is the more useful of the two -- an operating score should recover when the business recovers -- so filter each query to the last 30 days and keep the caption. If all-time is deliberate, the caption has to say so.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>The panel says 'Last 30 days - open anyone to see their full ops'. The service applies no date filter anywhere: tasks, decisions, invoices and the per-employee leaderboard are all queried for the whole tenant with no window at all. So an owner reads a colleague's score believing it reflects the last month, when it carries every task since the workspace opened -- somebody who was slow in August can never recover from it, and somebody who has improved this month does not show it.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>services/operating_score.py (all queries); the caption is in pages/OperatingScore.js, team-execution section</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -10652,7 +12351,7 @@
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -10662,12 +12361,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>'Do these first' on mobile</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -10675,24 +12374,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>On mobile the band should flow with the page rather than being pinned, so the score, the actions and the team list scroll as one column. If it must stay pinned, it needs to collapse to a handle the user can pull up.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>It is 90 per cent hidden. 'Do these first' occupies y=425 to 710, and a fixed black 'Team execution' band is pinned from y=454 to the bottom of the screen -- 374px, 46 per cent of the viewport -- covering 256 of its 285px. Scrolling does not help: the document itself does not scroll (scrollHeight equals clientHeight), and the element that does scroll is the dark band, not the page. So the three actions the page exists to recommend are permanently reduced to one visible line.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>pages/OperatingScore.js (kr-dark-band team-execution section)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -10705,7 +12404,7 @@
     <row r="30" ht="82" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -10715,12 +12414,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -10728,24 +12427,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Score each leg as a bounded rate rather than a penalty subtracted from a constant, so the number always has somewhere to move. Where a leg really is at the floor, say 'below floor' rather than printing a 0 that looks like an empty metric. See ASK-19 for the wider redesign.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>Two of the four legs are pinned at the floor and carry no information. Execution reads 0 and Responsiveness reads 0. Responsiveness actually computes to -296 before clamping (100 - 16 complaints x 12 - 68 overdue x 3), so it would take closing 8 complaints AND clearing 33 overdue tasks before the number moves off zero by a single point. The page's own advice is 'Close 16 open complaints' -- doing all of that would leave the score exactly where it is. The owner gets no gradient at precisely the moment they most need one.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>services/operating_score.py:_score_execution and the responsiveness expression in _company_operating_view</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -10758,7 +12457,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -10768,12 +12467,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -10788,17 +12487,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -10811,7 +12510,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -10821,12 +12520,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10841,17 +12540,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -10864,7 +12563,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -10874,12 +12573,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -10894,17 +12593,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -10917,7 +12616,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10927,12 +12626,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10947,17 +12646,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -10970,7 +12669,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -10980,12 +12679,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -11000,17 +12699,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -11023,7 +12722,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -11033,12 +12732,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -11046,24 +12745,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -11076,7 +12775,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -11086,12 +12785,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -11099,24 +12798,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -11129,7 +12828,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -11144,7 +12843,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -11152,24 +12851,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -11182,7 +12881,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -11197,7 +12896,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -11205,24 +12904,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -11235,7 +12934,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -11245,12 +12944,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -11258,24 +12957,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -11288,7 +12987,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -11298,12 +12997,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -11311,24 +13010,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -11341,7 +13040,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -11351,12 +13050,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -11364,24 +13063,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -11394,7 +13093,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -11404,12 +13103,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -11417,24 +13116,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -11447,7 +13146,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -11457,12 +13156,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -11470,24 +13169,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -11500,7 +13199,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -11515,7 +13214,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -11523,24 +13222,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -11553,7 +13252,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -11563,12 +13262,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -11576,24 +13275,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -11606,58 +13305,588 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>CR-07</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Contact profile - Log activity</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="82" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>OP-07</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Operating score - empty workspace</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="82" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>OP-08</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Category cards</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>pages/OperatingScore.js (category card progress track)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="82" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="82" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MW-14</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Page heading in the Leave / Workflows views</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="82" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="82" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="82" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="82" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="82" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="82" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K47"/>
+  <autoFilter ref="A1:K57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12605,7 +14834,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>116 (83 pass, 32 fail, 0 blocked, 1 not run)</t>
+          <t>135 (93 pass, 41 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -12617,7 +14846,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 6 High, 9 Medium, 5 Low, 7 Nit</t>
+          <t>1 Critical, 9 High, 13 Medium, 7 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3304,22 +3304,22 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3327,9 +3327,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -3339,47 +3339,47 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Visual / layout</t>
+          <t>Localisation</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Measured the grid that renders each role group on the team roster.</t>
+          <t>Read the rendered text of all six Overview tiles and compared it with what Intl produces for the same number in Indian grouping.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>A section holding one person does not leave two thirds of the row empty.</t>
+          <t>An India-first product groups rupees the Indian way, the same way everywhere.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+          <t>Tiles read 'Rs 2,685,000'; Intl.NumberFormat('en-IN') gives 'Rs 26,85,000'. Ledger.js:61 uses Intl.NumberFormat(undefined, ...).</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+          <t>Ledger.js defines its own private fmt() with an undefined locale, instead of the shared helper. lib/format.js already exports inr(), which uses en-IN and whose own docstring reads: 'no component formats currency inline -- everything goes through here.' Finance is the component that does.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -3387,22 +3387,22 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3410,9 +3410,9 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3422,47 +3422,47 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Information design</t>
+          <t>Truthfulness</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+          <t>Compared the number under the 'This month' chip with the API figure and with the date range of the underlying records.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+          <t>A figure captioned 'This month' covers this month.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+          <t>Hero binds {f(net)} where net = tt.net_profit; ledger_summary applies no date filter; sales invoices span 2026-06-14 to 2026-08-12.</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+          <t>The chip was written for a windowed figure the endpoint does not provide.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -3470,32 +3470,32 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Mobile + Desktop</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -3505,47 +3505,47 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Wrong data</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+          <t>Traced the series behind each trend percentage and recomputed it.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Each control in a dialog is distinguishable by name.</t>
+          <t>A trend shown beside Revenue describes revenue.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+          <t>months = summary.by_month, which ledger_summary builds by summing EXPENSES per month. pct(839469, 1077500) = -22.1%, exactly what the UI shows. netPoints = months.map(m =&gt; Number(m.net ?? m.amount ?? 0)) -- by_month carries no 'net' key, so every point silently falls through to the expense amount.</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+          <t>The frontend was written expecting by_month to carry a net figure per month. The backend never added one, and the ?? fallback turned a missing contract into a plausible-looking wrong number instead of an error.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -3553,22 +3553,22 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3576,239 +3576,654 @@
           <t>All</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Visual / alignment</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+          <t>Read what net_profit is composed of and compared it with a cash-basis calculation from the same records.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Cards sitting in the same row start their titles on the same line.</t>
+          <t>A figure called net profit is close to what an owner means by it.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+          <t>net_profit = revenue_billed - total_spend = 2685000 - 1946966 = 738034, verified against a recomputation. Cash basis (received - paid expenses) = 1936000 - 1291500 = 644500.</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+          <t>A simple difference was given the accounting term that sits closest to it.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Mobile + Desktop</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Loading state</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+          <t>Checked ledger_summary for any date filtering.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>While loading, the counter shows nothing, or a placeholder.</t>
+          <t>A finance dashboard can show a period.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+          <t>ledger_summary contains no date filter; every find() is {tenant_id} only, .to_list(5000).</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+          <t>The endpoint was built to summarise everything, and the period-aware UI arrived later.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
-        </is>
-      </c>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Visual / layout</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Measured the grid that renders each role group on the team roster.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>A section holding one person does not leave two thirds of the row empty.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>grid-template-columns resolves to three 437px tracks with a single child; the card occupies 437px of 1336px.</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>One grid definition is applied to every role group regardless of how many people it can contain.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="82" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Information design</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Compared what the page's own eyebrow promises with what the member cards actually show, for a member who has a reporting manager set.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>A roster headed EMPLOYEES / ACCESS / REPORTING LINES shows something of each at list level.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Card for a member with a manager reads: 'sai / csaicsai300@gmail.com / Active / 13 permissions'. Their profile dialog carries the manager and the full access list.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>The card was designed as an identity tile; the eyebrow describes the section's full remit, which only the dialog delivers.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="82" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Mobile + Desktop</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Enumerated the controls in a member profile dialog by accessible name.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Each control in a dialog is distinguishable by name.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Control inventory of the profile dialog for Priya Nair: ['Close', 'Edit access', 'Get invite link', 'Close'].</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>A custom close control was added at Team.js:530 while the dialog primitive still renders its own.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="82" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>MW-05</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Task list - bento grid</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Visual / alignment</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Measured the vertical offset of each card's title against its own card top, across the first four rows of the desktop grid.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Cards sitting in the same row start their titles on the same line.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Row 1: titleTop +56 / +17 / +17 with all three cards 161px tall.</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>The summary is a &lt;button&gt; with display:block that the grid stretches to the row height. A button's anonymous content box is centred vertically by the browser, so content shorter than the stretched button drifts to the middle.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: max title-top spread across a row is now 0px (was 39px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="82" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Loading state</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Switched the scope from My Tasks to All Tasks and watched the tab counters during the roughly 3 second fetch.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>While loading, the counter shows nothing, or a placeholder.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>t+300ms to t+1500ms: 16 skeletons rendered, tab text 'All 0'; at t+2500ms it becomes 'All 134'.</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>The counter renders the length of an empty list while the query is in flight instead of branching on the loading state.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED FIXED 2026-09-13 by re-running the original measurement: tab counter reads 'All -' while loading, then 'All 134' (was 'All 0').</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="82" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mobile + Desktop</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Owner / assignee</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Affordance</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>Created a task with 'evidence required', then pressed Complete with no proof attached, and checked whether the task completed.</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Completion is blocked until proof is attached.</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Toast: 'This task requires proof - add a photo, voice note, or file before completing.' Task remained in the active list afterwards.</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>complete() guards on evidence_required and returns a toast instead of the button carrying a disabled state.</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q38"/>
+  <autoFilter ref="A1:Q43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3819,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10053,12 +10468,12 @@
     <row r="127" ht="82" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-500</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10068,7 +10483,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -10078,12 +10493,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>/finance loads the Overview with six KPI tiles</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10093,7 +10508,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>Revenue billed, Received, Net profit, Total Spend, Asset Value, Inventory Value</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
@@ -10101,37 +10516,37 @@
     <row r="128" ht="82" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-501</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>All six tabs switch content</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10141,7 +10556,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>Overview, Revenue, Expenses, Assets, Inventory, Inbox all render</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
@@ -10149,37 +10564,37 @@
     <row r="129" ht="82" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-502</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>Every reported figure reconciles with a recomputation from raw records</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10189,7 +10604,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>8 of 8 reconcile to the paisa: billed 26,85,000; received 19,36,000; spend 19,46,966; paid 12,91,500; outstanding 6,55,466; assets 40,85,000; inventory 13,18,800; net 7,38,034</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
@@ -10197,37 +10612,37 @@
     <row r="130" ht="82" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-503</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Cross-tab consistency</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Desktop 1280x800</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>The same figure agrees across tabs</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10237,7 +10652,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>Overview 'Revenue billed' = Revenue tab 'Billed' = 26,85,000; status buckets (2 paid + 3 unpaid) sum to sales_count 5</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
@@ -10245,133 +10660,141 @@
     <row r="131" ht="82" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-504</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Money formatting</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Rupees are grouped the Indian way, consistently</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr"/>
+          <t>Tiles render Rs 2,685,000 instead of Rs 26,85,000, via a private formatter with an undefined locale; AI panels on the same page use Rs 7.49L</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>FN-01</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="82" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-505</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Net profit hero</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>A figure captioned 'This month' covers this month</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr"/>
+          <t>Shows the all-time 7,38,034 under a 'This month' chip</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>FN-02</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="82" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-506</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Trend badges</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>A trend beside Revenue describes revenue</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10381,49 +10804,49 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
+          <t>Both Revenue and Net profit trends are the month-on-month change in EXPENSES; pct(839469, 1077500) = -22.1%, exactly what is displayed</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-03</t>
         </is>
       </c>
     </row>
     <row r="134" ht="82" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-507</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>'Net profit' definition</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>The label matches the formula</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Metric design</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10433,113 +10856,653 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
+          <t>billed minus all expenses; no COGS, no inventory, assets ignored; cash basis differs by 93,534</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>FN-04</t>
         </is>
       </c>
     </row>
     <row r="135" ht="82" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-508</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Time window</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>The page can show a period</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Metric design</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr"/>
+          <t>No date filter anywhere; every figure is all-time</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>FN-05</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="82" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>T-509</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Revenue tab</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1280x800</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Billed / Received / Outstanding tiles are correct and unambiguous</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>26,85,000 / 19,36,000 / 7,49,000 - and 'Outstanding' here is receivables, distinct from the payables figure which is not shown as a tile</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="82" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>T-510</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Mobile quick actions</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 375x812</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>The capture row offers upload, scan, add and export</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Upload bill, Scan receipt, Add expense, Export all render</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138" ht="82" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="82" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140" ht="82" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Production sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" ht="82" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Finance sees a narrowed set scoped to their role</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" ht="82" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Page load</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>All four</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>No uncaught page errors for any persona</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="82" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Console + network</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>No application console errors and no failing API calls in normal use</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144" ht="82" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="82" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="82" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147" ht="82" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J136"/>
+  <autoFilter ref="A1:J147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10788,7 +11751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12457,7 +13420,7 @@
     <row r="31" ht="82" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MW-03</t>
+          <t>FN-01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -12467,12 +13430,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Header - global search (Cmd+K)</t>
+          <t>Every money figure</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -12480,24 +13443,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
+          <t>Delete the private fmt() and import inr from lib/format. The helper already exists and already does the right thing, so this is an import swap rather than a rewrite. Worth a lint rule banning Intl.NumberFormat with a currency style outside lib/format.js.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
+          <t>Finance renders 2685000 as Rs 2,685,000 -- Western thousands grouping. Indian convention is Rs 26,85,000. Every tile is affected: Asset Value shows Rs 4,085,000 for what an Indian owner reads as Rs 40,85,000. Worse than being consistently wrong, it is inconsistent: the AI panels ON THE SAME PAGE correctly say 'Rs 7.49L' and 'Rs 13.18 L', and CRM cards elsewhere show 'Rs 4,00,000'. And because the locale is left undefined, the grouping follows each viewer's browser -- the same figure renders differently for different people.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
+          <t>pages/Ledger.js:61-64 (private fmt); lib/format.js:19-30 (inr, and the rule it states)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -12510,7 +13473,7 @@
     <row r="32" ht="82" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MW-04</t>
+          <t>FN-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -12520,12 +13483,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker (mobile)</t>
+          <t>Net profit hero (mobile)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -12533,24 +13496,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
+          <t>Either compute a monthly net and show that, or drop the chip. The backend already buckets by month for expenses, so half the machinery exists -- it needs the revenue side to match (see FN-03).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
+          <t>It is the all-time figure. The hero shows Rs 738,034 beneath a chip reading 'This month', and 738034 is exactly net_profit from the API, which is computed with no date filter over records spanning June to August. So an owner glancing at their phone reads a lifetime number as a monthly one -- and on a money screen that is the kind of mistake that gets acted on.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>components/mobile/DexFab.jsx:70-82</t>
+          <t>pages/Ledger.js:1005 (net), :1042 ('This month' chip), :1048 (the value)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -12563,7 +13526,7 @@
     <row r="33" ht="82" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MW-11</t>
+          <t>FN-03</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -12573,12 +13536,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toolbar in the Leave / Workflows views</t>
+          <t>Revenue and Net profit trend badges (mobile)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -12586,24 +13549,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
+          <t>Have ledger_summary return revenue and net per month alongside expenses, and bind each trend to its own series. Until then the honest move is to hide the badges rather than show a number that means something else -- and drop the ?? fallback, which is what let this ship silently.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
+          <t>Both trend badges are computed from EXPENSES. The Revenue tile reads 'Rs 2,685,000, down 22.1%' -- but that 22.1% is the month-on-month fall in SPENDING, from Rs 10,77,500 in July to Rs 8,39,469 in August. Revenue did not fall; costs did, which is usually good news being reported in red as bad. The Net profit trend is the same number from the same series.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
+          <t>pages/Ledger.js:1009-1015 (months, netPoints, netTrend), :1061 (revenue trend); routers/ledger.py:1237-1245 (by_month is expenses only)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -12616,7 +13579,7 @@
     <row r="34" ht="82" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MW-12</t>
+          <t>MW-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -12626,12 +13589,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Leave and Workflows entry points</t>
+          <t>Header - global search (Cmd+K)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -12646,17 +13609,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
+          <t>Inside CommandDialog, wrap a DialogTitle (and a DialogDescription) in the VisuallyHidden primitive so the dialog is named for assistive tech without changing the visual design.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
+          <t>The dialog exposes aria-labelledby pointing at an element id that does not exist, so it is announced with no name. Radix logs an error every time it opens. Reproduces on My Work and on Finance, so it affects every screen.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
+          <t>components/ui/command.jsx:19 (used at components/Layout.js:599)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -12669,7 +13632,7 @@
     <row r="35" ht="82" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>MW-04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -12679,12 +13642,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Member profile - ACCESS block</t>
+          <t>Dex FAB picker (mobile)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -12699,17 +13662,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
+          <t>Close the picker on Escape - either a keydown listener while picker is open, or render it inside a Radix DismissableLayer / Popover so dismissal, focus trapping and aria come from the same primitive the other sheets already use.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
+          <t>Escape does nothing - the menu stays open and its full-screen scrim keeps blocking the page underneath. Only a pointer tap outside closes it. There is also no focus trap, so keyboard focus walks behind the open menu.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
+          <t>components/mobile/DexFab.jsx:70-82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -12722,7 +13685,7 @@
     <row r="36" ht="82" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TM-06</t>
+          <t>MW-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -12732,12 +13695,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Add member - all form fields</t>
+          <t>Toolbar in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -12752,17 +13715,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
+          <t>Render the task-scope controls only while view === 'mywork'. Leave the view toggle itself (Workflows / Leave) in place, since that is how you get back. If a scope control must stay, it should not silently change view - that side effect is what makes it feel broken.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
+          <t>Four task-only controls stay visible in both views - New Task, My Tasks, All Tasks and AI Priority - none of which mean anything for leave or for pipelines. Worse, pressing My Tasks, All Tasks or AI Priority silently throws you back to the task list, losing the view you were in with no warning. In the Leave view 'New Task' is also the largest, darkest button on screen, and it creates a task, not a leave request.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
+          <t>pages/MyWork.js:2429-2515 (mywork-controls / work-view-toggle); handlers at 2442, 2448, 2463</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -12775,7 +13738,7 @@
     <row r="37" ht="82" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CR-02</t>
+          <t>MW-12</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -12785,12 +13748,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - all fields</t>
+          <t>Leave and Workflows entry points</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -12805,17 +13768,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
+          <t>Pick one home per feature and use it on both viewports. Given Leave already has its own route and its own mobile tile, the cheaper and more consistent direction is to make the standalone page the home on desktop too - see the note on MW-11 about how little of Leave actually belongs in My Work.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
+          <t>Neither toggle is reachable on mobile - both are in the DOM but hidden, so from My Work there is no way into Leave or Workflows on a phone. They are reachable, but from somewhere else entirely: the 'More' panel lists them as their own destinations. So the same two features are sub-views of My Work on desktop and separate destinations on mobile.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
+          <t>pages/MyWork.js:2476 (work-view-toggle); components/mobile/AllAppsPanel.jsx</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -12828,7 +13791,7 @@
     <row r="38" ht="82" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CR-06</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -12838,12 +13801,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Contact cards (mobile)</t>
+          <t>Member profile - ACCESS block</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -12858,17 +13821,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
+          <t>Gate the whole ACCESS section, not just its button. This is the same change the founder asked for in ASK-13 and ASK-15, so treat them as one piece of work: hide access on the roster, and show the section only to people who hold the permission that governs it.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
+          <t>Every role can read every other member's complete permission matrix. Production and Finance -- who hold neither team_manage nor people -- can open Priya Nair's card and see '6 permissions', then inside: '6 of 14 areas', the granted chips, and the full denial list naming every area she cannot reach. Only the Edit access BUTTON is gated to the owner; viewing is not gated at all.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:940-1050 (contact card grid)</t>
+          <t>pages/Team.js:411 + :441 (card count), :580-606 (ACCESS block, granted-perms and the denial list)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -12881,7 +13844,7 @@
     <row r="39" ht="82" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CR-08</t>
+          <t>TM-06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -12891,12 +13854,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Contact profile (mobile) - In progress list</t>
+          <t>Add member - all form fields</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -12911,17 +13874,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
+          <t>Give all six a real label with htmlFor pointing at the input's id. Keep placeholders for examples ('e.g. 98765 43210'), not for the field name. This is part of the ASK-14 redesign but is worth doing even if that redesign is deferred -- it is a few lines and it is the difference between the form being usable with a screen reader and not.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
+          <t>Not one of the six fields has a programmatic label. Name, Email, Temp password and Mobile number are placeholder-only, so the field name disappears the moment anything is typed -- a sighted user who tabs away and back cannot tell which box is which. Role and Reporting Manager LOOK labelled, but their text is not associated with the control, so a screen reader gets nothing from them either.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
+          <t>pages/Team.js:120, :121, :129, :132 (placeholder-only), :137-138 and :143-144 (unassociated labels)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -12934,7 +13897,7 @@
     <row r="40" ht="82" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>CR-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -12944,12 +13907,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>'Sales' category</t>
+          <t>Add contact dialog - all fields</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -12964,17 +13927,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
+          <t>Associate a real label with every field here and in Team's Add member (TM-06). Worth doing as one pass over both dialogs rather than twice, and worth adding a lint rule or a test so the next form starts labelled.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
+          <t>None of the six fields has a label of any kind - the dialog contains no label elements at all. Name, Company, Phone and Email are placeholder-only, and the two selects have nothing naming them. This is the same defect as TM-06 in Team, in a different dialog, which makes it a pattern across the app rather than a one-off.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_sales</t>
+          <t>pages/CRM.js:282 (crm-contact-name), :313 (lifecycle), and the four unlabelled inputs between them</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -12987,7 +13950,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>CR-06</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -12997,12 +13960,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact cards (mobile)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -13017,17 +13980,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
+          <t>Go single column under about 480px, matching Team. If two columns are wanted on larger phones, drop the company line and the touched line to keep the name whole.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
+          <t>The grid stays two columns on a 375px screen, giving each card 161px. Eight text nodes truncate as a result, including the customer names themselves -- 'Krishna Garments Pvt Ltd' needs 144px and gets 114, 'Anand Fabrics' needs 88 and gets 76. Supporting lines like '6 open complaints' and 'Touched 29 days ago' wrap onto two lines, and the card heights go ragged. Team's roster drops to a single column on the same screen and reads cleanly, so the app already has the better answer.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
+          <t>pages/CRM.js:940-1050 (contact card grid)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -13040,7 +14003,7 @@
     <row r="42" ht="82" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>OP-06</t>
+          <t>CR-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -13050,12 +14013,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Operating score model</t>
+          <t>Contact profile (mobile) - In progress list</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -13070,17 +14033,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
+          <t>Guard on the value, not on the humaniser: render the human date when there is one, the raw date only when the value exists but will not parse, and nothing at all when there is no date. Worth grepping for the same `|| \`... ${value}\`` shape elsewhere -- this pattern fails the same way wherever it appears.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
+          <t>The literal word 'undefined' is printed to the user: two rows read 'Due undefined - Rs 1' and 'Due undefined - Rs 6,00,000'. It is the kind of thing a customer screenshots.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py:_company_operating_view</t>
+          <t>pages/mobile/ContactProfileMobile.jsx:215 (fallback), :24 (humanDate)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -13093,7 +14056,7 @@
     <row r="43" ht="82" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>OP-09</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -13108,7 +14071,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>'View all' links and the formula panel (mobile)</t>
+          <t>'Sales' category</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -13123,17 +14086,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
+          <t>Rename it to what it measures -- Decision velocity, or Approvals -- which is a genuinely good metric for a decision OS. If a real Sales leg is wanted, invoices already carry the data for revenue this period against last.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
+          <t>It is the share of DECISIONS that have been approved -- approved/total x 100 -- and contains no revenue, no orders, no pipeline and no customer. On live data it reads 22 because 17 of 77 decisions are approved. An owner could sell nothing all month and lift 'Sales' by approving decisions, or have a record month and watch it fall because approvals are backed up. The number is real and useful; the label is the wrong one.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
+          <t>services/operating_score.py:_score_sales</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -13146,7 +14109,7 @@
     <row r="44" ht="82" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MW-13</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -13156,12 +14119,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Workflows view - pipeline cards</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -13169,24 +14132,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
+          <t>Pick one home for lateness. Execution is the natural one; Responsiveness should be about complaints and reply time, which is what its name promises.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
+          <t>One overdue task is charged twice: it raises the overdue ratio inside Execution (x40 of the ratio) and is also subtracted directly from Responsiveness (x3 per task). Those two legs are 35 and 20 per cent of the overall score, so lateness quietly drives 55 per cent of it. On the live tenant that is -20.9 on one leg and -204 on the other.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
+          <t>services/operating_score.py:_score_execution and _company_operating_view</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -13199,7 +14162,7 @@
     <row r="45" ht="82" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>OP-06</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -13209,12 +14172,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Add member - login method toggle</t>
+          <t>Operating score model</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -13222,24 +14185,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
+          <t>Express each as a rate against the relevant denominator -- complaints per active customer, overdue as a share of open work, overdue invoices as a share of open invoices -- so the score means the same thing at any size.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
+          <t>Three penalties are absolute rather than proportional: complaints x12, overdue x3, overdue invoices x5. A five-person shop with 9 open complaints scores 0 on Responsiveness; so does a 500-person company with 9. As a tenant grows, the score falls for reasons that have nothing to do with how well it is run, and the metric stops being comparable with its own past.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
+          <t>services/operating_score.py:_company_operating_view</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -13252,7 +14215,7 @@
     <row r="46" ht="82" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>OP-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -13262,12 +14225,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Scope chips (Buyers / Suppliers)</t>
+          <t>'View all' links and the formula panel (mobile)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -13275,24 +14238,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
+          <t>Fixing OP-02 -- letting the page scroll as one column on mobile -- makes the formula panel reachable on its own. The View all links still need to grow to 24px minimum and to sit clear of the Dex button's safe area.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
+          <t>Three problems, all downstream of the page not scrolling on mobile. The two 'View all' links measure 61x20, under the 24px minimum, and the first of them is physically covered by the floating Dex button. The 'How is this calculated' formula panel sits at y=1153 on an 812px screen and cannot be reached at all, so the one place that explains where the score comes from is invisible on a phone -- which matters more than usual here, given two of the four legs read 0.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
+          <t>pages/OperatingScore.js (View all links, operating-formula-toggle)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -13305,7 +14268,7 @@
     <row r="47" ht="82" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CR-07</t>
+          <t>FN-04</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -13315,12 +14278,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Contact profile - Log activity</t>
+          <t>'Net profit' tile</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -13328,24 +14291,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
+          <t>Rename to something the formula actually supports -- 'Billed minus spend', or 'Gross margin (billed)' -- or compute a real net that accounts for COGS and inventory. The former is a one-line change and stops the page overclaiming.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
+          <t>It is revenue BILLED minus ALL recorded expenses, including expenses not yet paid. It subtracts no cost of goods and no inventory movement, and ignores assets entirely -- Rs 40,85,000 of them. On live data it reports Rs 7,38,034, where the cash-basis figure is Rs 6,44,500, a gap of Rs 93,534. The arithmetic is right; the name is doing more work than the formula can support.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>pages/ContactProfile.js (Log button and page background)</t>
+          <t>routers/ledger.py:1257 (net_profit); pages/Ledger.js:566-573 (the tile)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -13358,7 +14321,7 @@
     <row r="48" ht="82" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>OP-07</t>
+          <t>FN-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -13368,12 +14331,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Operating score - empty workspace</t>
+          <t>All figures</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13381,24 +14344,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
+          <t>Accept a period parameter (this month, this quarter, this FY -- the Indian financial year matters here) and filter each query by it, defaulting to the current month. That single change also gives FN-02 and FN-03 the data they are currently faking.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
+          <t>Every figure is all-time and there is no way to change that. Expenses, invoices, payments, assets and inventory are each queried for the whole tenant with no window and capped at 5000 records. So the page can tell an owner what they have billed since the company started, but not what they billed this month -- which is the question a finance screen is opened to answer. It is also why FN-02's 'This month' chip has nothing to bind to.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
+          <t>routers/ledger.py:1223-1262 (ledger_summary)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -13411,7 +14374,7 @@
     <row r="49" ht="82" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>OP-08</t>
+          <t>MW-13</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -13421,12 +14384,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Category cards</t>
+          <t>Workflows view - pipeline cards</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -13441,17 +14404,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
+          <t>Give each an aria-label that names its card, e.g. 'Delete card: Dispatch 100 sales items today'. The card title is already to hand where the button is rendered.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
+          <t>Five separate buttons are all named exactly 'Delete card', and two are both named 'Advance to Delivered'. Sighted users tell them apart by which card they sit on; a screen-reader user hears the same phrase five times with nothing to say which shipment is about to be deleted. Deletion is the most destructive action in the view, which is what lifts this above cosmetic.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>pages/OperatingScore.js (category card progress track)</t>
+          <t>pages/Workflows.js (delete-workflow-* and advance-workflow-* buttons)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -13464,7 +14427,7 @@
     <row r="50" ht="82" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MW-05</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -13474,12 +14437,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Task list - bento grid</t>
+          <t>Add member - login method toggle</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -13494,17 +14457,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
+          <t>Add aria-pressed to both buttons, and wrap them in a role='group' with an accessible label such as 'Login method' - matching the permission grid immediately below it.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
+          <t>Neither half carries aria-pressed. The selection is conveyed only by a class swap (kr-pressed against kr-pop), so a sighted user sees which method is active and a screen-reader user hears two identical unlabelled buttons. Choosing between a password and an OTP decides how that person will sign in for good, so it is worth announcing.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
+          <t>pages/Team.js:122-127 (login-method-toggle); the pattern to copy is at :165</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -13517,7 +14480,7 @@
     <row r="51" ht="82" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MW-14</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -13527,12 +14490,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Page heading in the Leave / Workflows views</t>
+          <t>Scope chips (Buyers / Suppliers)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13540,24 +14503,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
+          <t>Add aria-pressed to the desktop chips, mirroring the mobile pair, and give the row a role='group' with a label. Same family as TM-01.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
+          <t>The desktop chips carry no aria-pressed at all, while the mobile twins of the same control set it correctly (true on Buyers, false on Suppliers). So the identical control is announced properly on a phone and not on a laptop. The filtering itself is correct - Buyers shows 11, Suppliers shows 6, and switching back restores 11.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
+          <t>pages/CRM.js:819-836 (crm-scope-chips, desktop); the correct pattern is at :794-805 (crm-scope-mobile)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -13570,7 +14533,7 @@
     <row r="52" ht="82" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>CR-03</t>
+          <t>CR-07</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -13585,7 +14548,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Add contact dialog - dismiss controls</t>
+          <t>Contact profile - Log activity</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13593,24 +14556,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+          <t>Repaint Log with the standard primary, and check the contact profile's background against the list it is reached from -- a detail page changing ground colour makes the two feel like separate apps.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+          <t>The Log button on the contact profile is indigo, rgb(55,58,205), while every other primary action in the app -- Add contact, Add member, Complete, Approve -- is the near-black ink colour. Contrast is fine at 7.93:1; the problem is that it reads as a different product for a moment. The contact profile also sits on a strong amber gradient while the CRM list it came from is neutral grey, which compounds the shift.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+          <t>pages/ContactProfile.js (Log button and page background)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -13623,7 +14586,7 @@
     <row r="53" ht="82" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>OP-07</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -13633,12 +14596,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Owner section grid</t>
+          <t>Operating score - empty workspace</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -13646,24 +14609,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+          <t>Keep the neutral internal default if it helps the maths, but let the UI show 'not enough data yet' rather than a score, using the enough_data flag that is already computed and sent.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+          <t>Completion, approval rate and collection rate each fall back to 0.7 when there is nothing to divide by, so a brand-new tenant that has done nothing at all scores about 70 out of 100 and is told it is doing reasonably well. There is an enough_data flag in the payload, so the page can already tell the difference -- the default just makes the number look earned.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+          <t>services/operating_score.py (the 0.7 defaults, enough_data)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -13676,7 +14639,7 @@
     <row r="54" ht="82" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>OP-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -13686,12 +14649,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Member cards</t>
+          <t>Category cards</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -13699,24 +14662,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+          <t>Give a floored score its own treatment -- a filled track in the warning colour, or an explicit 'at floor' marker -- so it reads as a measured bad result rather than an absent one.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+          <t>Execution and Responsiveness both render '0 / 100' above a completely empty progress bar, which is pixel-identical to how an unmeasured category would look. Two of the four cards on the page therefore read as 'nothing here' when they actually mean 'this is as bad as it gets'.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+          <t>pages/OperatingScore.js (category card progress track)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -13729,7 +14692,7 @@
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TM-04</t>
+          <t>MW-05</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -13739,12 +14702,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Member profile dialog</t>
+          <t>Task list - bento grid</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -13752,24 +14715,24 @@
           <t>Bug fix</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Nit</t>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+          <t>Make the button a column flex container and pin content to the top - add 'flex flex-col justify-start' to its className. Verified live in the browser: all three titles then start at 17px.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+          <t>Titles in one row start at different heights - the spread was 39px, 17px, 11px and 17px across the first four rows. A short title sinks toward the middle of its card while a long one starts at the top, so the row reads as ragged. The checkboxes stay aligned, which makes it more obvious.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>pages/Team.js:497-535 (profile dialog header)</t>
+          <t>pages/MyWork.js:1181 (the task-summary button className)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -13782,7 +14745,7 @@
     <row r="56" ht="82" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MW-06</t>
+          <t>MW-14</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -13797,7 +14760,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Category tab bar</t>
+          <t>Page heading in the Leave / Workflows views</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -13812,17 +14775,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+          <t>Swap the heading with the view - 'Leave' or 'Workflows' - or append the view name. Only worth doing if the views stay inside My Work at all; see MW-12.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+          <t>The heading stays 'My Work' with the eyebrow 'YOUR DAY, SIMPLIFIED' even when the body is entirely leave requests or delivery pipelines. Nothing above the fold says which of the three views is active except the small toggle pill.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+          <t>pages/MyWork.js (page header, above the view switch at 2527)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -13835,58 +14798,323 @@
     <row r="57" ht="82" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>CR-03</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Add contact dialog - dismiss controls</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention for the whole app - most products keep the X and drop the Cancel, or keep Cancel on destructive-ish forms only - and apply it to both this dialog and TM-04.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Two: a 'Cancel' button beside Add contact, and a separate 'Close' X. Team's profile dialog has the same duplication (TM-04), so it is worth settling once for the app rather than per dialog.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>pages/CRM.js:242-365 (crm-contact-dialog footer)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="82" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TM-02</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Owner section grid</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Either let a single-card group span the row, or give the owner its own treatment at the top of the page - it is a different kind of row from a department, and looks like one.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>The Owner group uses the same three-column grid as every other role but will almost always hold exactly one card, so 874px of a 1336px row is blank. It reads as a rendering fault rather than a deliberate space.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:366 (team-cards-&lt;role&gt; grid)</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="82" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Member cards</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Put the reporting line on the card - one line, 'Reports to Sunita Rao' - and consider replacing the bare count with the two or three areas that distinguish this person, keeping the full list in the dialog. Cheapest alternative: soften the eyebrow so it stops promising what the list does not show.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>The cards show name, email, status and a permission COUNT. The reporting line is absent entirely, and access is reduced to a number that says nothing about what the person can reach. Both exist one click deeper - the profile dialog reads 'REPORTS TO Sunita Rao' and '13 of 14 areas' with the areas listed - so the data is there and simply is not surfaced where the page says it will be.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:417-450 (member card); manager already resolved at :475</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="82" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TM-04</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Member profile dialog</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Keep one. If the custom 36px control is the intended one, hide the primitive's default close for this dialog.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Two separate visible buttons are both named exactly 'Close'. A screen-reader user tabbing the dialog meets the same name twice with nothing to separate them.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>pages/Team.js:497-535 (profile dialog header)</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="82" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>MW-06</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>UI audit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Category tab bar</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Nit</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>While the tasks query is loading, render a dash or omit the count, matching the skeleton treatment already used for the cards below.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>The tab reads 'All 0' for the whole fetch, which states a count of zero rather than an unknown one. The card skeletons underneath are correct, so the count is the only misleading element.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js:2556-2566 (work-tabs counts)</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="82" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>MW-07</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>UI audit</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Task card - Complete (evidence required)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>By design</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
         <is>
           <t>Nit</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Optional polish only: disable Complete while proof is missing and put the reason in a tooltip or helper line, so the constraint is visible before the click rather than after it. Current behaviour is safe and correct.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Completion IS correctly blocked - the task stays in the active list and an explanatory toast appears. The only nit is that the button looks available and only explains itself after it is pressed.</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>pages/MyWork.js:1107-1119</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>Not a defect</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14834,7 +16062,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>135 (93 pass, 41 fail, 0 blocked, 1 not run)</t>
+          <t>146 (99 pass, 46 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
@@ -14846,7 +16074,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>1 Critical, 9 High, 13 Medium, 7 Low, 7 Nit</t>
+          <t>1 Critical, 12 High, 15 Medium, 7 Low, 7 Nit</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_UI_Bug_Report.xlsx
+++ b/docs/DecisionOS_UI_Bug_Report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Log'!$A$1:$Q$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Coverage'!$A$1:$J$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Verified Non-Issues'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action List'!$A$1:$K$62</definedName>
   </definedNames>
@@ -4234,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11016,22 +11016,22 @@
     <row r="138" ht="82" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>T-070</t>
+          <t>T-511</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Control sweep</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
+          <t>Every control pressed without crashing the app</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
+          <t>37 checks passed across both viewports; 0 crashes; 8 mutations blocked including POST ledger/ai/brief/refresh</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
@@ -11064,37 +11064,37 @@
     <row r="139" ht="82" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>T-071</t>
+          <t>T-512</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>KPI tiles as links</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Sales sees their own work and no cross-tenant scope switch</t>
+          <t>Each KPI tile navigates to its tab</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
+          <t>mkpi-revenue is an &lt;a href='/finance?tab=revenue'&gt;; clicking moves the URL from '' to '?tab=revenue'. The sweep first flagged all 14 tiles as dead - a false positive from comparing only the path, now fixed in the harness</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
@@ -11112,37 +11112,37 @@
     <row r="140" ht="82" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>T-072</t>
+          <t>T-513</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Page load</t>
+          <t>Mobile tab strip</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Desktop 1440x900</t>
+          <t>Mobile 375x812</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Production sees a narrowed set scoped to their role</t>
+          <t>The six tabs are reachable on a phone</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
+          <t>Horizontally scrollable strip: scrollWidth 639 &gt; clientWidth 446, overflow-x auto. The sweep first reported a 130px spill - a false positive on a deliberately scrollable strip, now excluded in the harness</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
     <row r="141" ht="82" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>T-073</t>
+          <t>T-070</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -11180,12 +11180,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Finance sees a narrowed set scoped to their role</t>
+          <t>Owner sees all tasks, can create, and gets the All Tasks scope</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+          <t>28 tasks; create yes; all-scope yes; tabs all/sales/logistics/hr/completed</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
@@ -11208,7 +11208,7 @@
     <row r="142" ht="82" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>T-074</t>
+          <t>T-071</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>All four</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>No uncaught page errors for any persona</t>
+          <t>Sales sees their own work and no cross-tenant scope switch</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>0 page errors across owner, sales, production and finance</t>
+          <t>29 tasks; create yes; all-scope no; tabs all/sales/finance/completed</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
@@ -11256,7 +11256,7 @@
     <row r="143" ht="82" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>T-080</t>
+          <t>T-072</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -11266,27 +11266,27 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Console + network</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>No application console errors and no failing API calls in normal use</t>
+          <t>Production sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
+          <t>12 tasks; create yes; all-scope no; tabs all/production/finance</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
@@ -11304,17 +11304,17 @@
     <row r="144" ht="82" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>T-081</t>
+          <t>T-073</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Global search dialog</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -11324,91 +11324,83 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Opening global search logs no accessibility errors</t>
+          <t>Finance sees a narrowed set scoped to their role</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Radix logs a missing DialogTitle error on every open</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>MW-03</t>
-        </is>
-      </c>
+          <t>13 tasks; create yes; all-scope no; tabs all/finance</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
     </row>
     <row r="145" ht="82" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>T-082</t>
+          <t>T-074</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Dex FAB picker</t>
+          <t>Page load</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Desktop 1440x900</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>All four</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>The picker closes on Escape</t>
+          <t>No uncaught page errors for any persona</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Escape is ignored; only a pointer tap dismisses it</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>MW-04</t>
-        </is>
-      </c>
+          <t>0 page errors across owner, sales, production and finance</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
     </row>
     <row r="146" ht="82" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>T-083</t>
+          <t>T-080</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -11418,12 +11410,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Control sweep</t>
+          <t>Console + network</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Mobile 390x844</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -11433,7 +11425,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Every non-destructive control responds without breaking the page</t>
+          <t>No application console errors and no failing API calls in normal use</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -11448,7 +11440,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>13 controls exercised, 0 click failures, page never blanked</t>
+          <t>Only the pre-login 401 on /auth/me, which is the app discovering it has no session yet</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -11456,53 +11448,205 @@
     <row r="147" ht="82" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Global search dialog</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Desktop 1440x900</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Opening global search logs no accessibility errors</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Radix logs a missing DialogTitle error on every open</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>MW-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="82" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Dex FAB picker</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>The picker closes on Escape</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Escape is ignored; only a pointer tap dismisses it</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>MW-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="82" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Control sweep</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Mobile 390x844</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Every non-destructive control responds without breaking the page</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>13 controls exercised, 0 click failures, page never blanked</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150" ht="82" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
           <t>T-084</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>My Work</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Control sweep</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Desktop 1440x900</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Every non-destructive control responds without breaking the page</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Stability</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr">
+      <c r="H150" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>24 controls exercised, 0 click failures, page never blanked</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J147"/>
+  <autoFilter ref="A1:J150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16062,7 +16206,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>146 (99 pass, 46 fail, 0 blocked, 1 not run)</t>
+          <t>149 (102 pass, 46 fail, 0 blocked, 1 not run)</t>
         </is>
       </c>
     </row>
